--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -19131,3594 +18995,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>壹沐第1期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>401 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>399 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Q</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>33/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 832呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>B | 348呎 (2房)
-$814万
-$23,388/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$818万
-$23,439/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr">
-        <is>
-          <t>D | 350呎 (2房)
-$822万
-$23,490/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr">
-        <is>
-          <t>E | 269呎 (1房)
-$632万
-$23,507/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$634万
-$23,552/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>G | 379呎 (2房)
-$962万
-$25,377/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>H | 320呎 (2房)
-$712万
-$22,259/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J6" s="17" t="inlineStr">
-        <is>
-          <t>J | 269呎 (1房)
-$589万
-$21,894/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="K6" s="17" t="inlineStr">
-        <is>
-          <t>K | 272呎 (1房)
-$596万
-$21,928/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="L6" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$598万
-$22,000/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="M6" s="17" t="inlineStr">
-        <is>
-          <t>M | 271呎 (1房)
-$593万
-$21,881/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N6" s="19" t="inlineStr"/>
-      <c r="O6" s="19" t="inlineStr"/>
-      <c r="P6" s="19" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>32/F</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$1,003万
-$21,571/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$825万
-$23,632/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$785万
-$22,488/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$712万
-$20,409/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$744万
-$21,246/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G7" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$596万
-$22,162/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H7" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$588万
-$21,873/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$865万
-$22,815/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J7" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$662万
-$20,672/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K7" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$547万
-$20,333/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L7" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$531万
-$19,516/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M7" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$561万
-$20,632/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N7" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$572万
-$21,044/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O7" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$566万
-$21,121/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P7" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$807万
-$21,981/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>31/F</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$924万
-$19,879/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$749万
-$21,457/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$725万
-$20,776/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E8" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$697万
-$19,958/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$712万
-$20,332/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$571万
-$21,230/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$564万
-$20,956/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$808万
-$21,306/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J8" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$632万
-$19,746/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K8" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$550万
-$20,454/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L8" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$510万
-$18,748/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="M8" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$536万
-$19,710/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N8" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$547万
-$20,102/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O8" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$541万
-$20,169/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P8" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$779万
-$21,233/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$929万
-$19,989/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$745万
-$21,334/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$721万
-$20,658/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E9" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$693万
-$19,844/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$745万
-$21,298/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$598万
-$22,245/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$552万
-$20,507/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$803万
-$21,184/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J9" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$630万
-$19,690/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K9" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$523万
-$19,460/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$522万
-$19,199/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$563万
-$20,703/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$545万
-$20,044/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$539万
-$20,109/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P9" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$769万
-$20,947/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$940万
-$20,207/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$740万
-$21,213/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$717万
-$20,540/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E10" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$689万
-$19,731/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$704万
-$20,102/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$565万
-$20,997/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$540万
-$20,061/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$760万
-$20,061/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J10" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$628万
-$19,632/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K10" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$519万
-$19,301/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$493万
-$18,136/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$539万
-$19,807/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$573万
-$21,054/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$543万
-$20,265/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P10" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$767万
-$20,886/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$914万
-$19,657/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$740万
-$21,213/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$717万
-$20,540/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E11" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$711万
-$20,374/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$704万
-$20,102/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$565万
-$20,997/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$558万
-$20,726/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$790万
-$20,841/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J11" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$628万
-$19,632/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K11" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$519万
-$19,301/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$493万
-$18,136/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$533万
-$19,597/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$544万
-$19,985/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$540万
-$20,157/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P11" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$808万
-$22,003/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$909万
-$19,544/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$732万
-$20,966/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$709万
-$20,305/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$703万
-$20,143/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$703万
-$20,085/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$588万
-$21,875/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$551万
-$20,497/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$781万
-$20,602/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J12" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$624万
-$19,515/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K12" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$516万
-$19,187/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$529万
-$19,432/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$536万
-$19,689/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$540万
-$19,869/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$534万
-$19,931/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P12" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$803万
-$21,874/呎
-(26年-05月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$899万
-$19,326/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$713万
-$20,439/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$715万
-$20,492/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E13" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$699万
-$20,026/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$688万
-$19,652/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$555万
-$20,650/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$548万
-$20,382/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$804万
-$21,206/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J13" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$626万
-$19,561/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="K13" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$515万
-$19,128/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$511万
-$18,776/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$534万
-$19,629/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$568万
-$20,869/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$533万
-$19,872/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P13" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$760万
-$20,702/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$933万
-$20,069/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$709万
-$20,318/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$711万
-$20,374/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E14" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$658万
-$18,861/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$662万
-$18,908/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$552万
-$20,532/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$551万
-$20,484/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$799万
-$21,083/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J14" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$619万
-$19,343/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K14" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$511万
-$19,013/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$489万
-$17,967/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$525万
-$19,308/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$536万
-$19,693/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$532万
-$19,856/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P14" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$758万
-$20,641/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$933万
-$20,058/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$705万
-$20,200/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$707万
-$20,254/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E15" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$654万
-$18,750/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$658万
-$18,800/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$549万
-$20,417/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$542万
-$20,153/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$794万
-$20,960/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J15" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$655万
-$20,460/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K15" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$508万
-$18,898/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$488万
-$17,959/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$528万
-$19,397/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$561万
-$20,619/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$526万
-$19,631/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P15" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$741万
-$20,180/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$883万
-$18,993/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$727万
-$20,837/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$700万
-$20,045/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E16" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$687万
-$19,675/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$654万
-$18,689/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$557万
-$20,702/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$539万
-$20,038/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$790万
-$20,836/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="J16" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$646万
-$20,192/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K16" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$507万
-$18,842/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$482万
-$17,709/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$531万
-$19,514/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$531万
-$19,514/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$525万
-$19,572/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P16" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$742万
-$20,226/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$878万
-$18,883/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$686万
-$19,662/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D17" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$688万
-$19,715/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E17" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$647万
-$18,529/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$650万
-$18,579/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$554万
-$20,584/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$536万
-$19,923/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$785万
-$20,713/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J17" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$595万
-$18,601/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K17" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$505万
-$18,783/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$486万
-$17,852/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$529万
-$19,456/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$558万
-$20,497/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$523万
-$19,513/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P17" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$736万
-$20,060/呎
-(26年-04月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$850万
-$18,283/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$682万
-$19,544/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D18" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$691万
-$19,807/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$678万
-$19,441/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$646万
-$18,468/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G18" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$551万
-$20,465/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H18" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$533万
-$19,809/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$725万
-$19,142/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="J18" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$600万
-$18,748/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K18" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$504万
-$18,728/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L18" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$505万
-$18,581/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M18" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$528万
-$19,398/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N18" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$528万
-$19,398/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O18" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$521万
-$19,453/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P18" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$734万
-$19,999/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$916万
-$19,699/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$678万
-$19,426/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="D19" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$680万
-$19,479/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$646万
-$18,513/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$678万
-$19,377/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$547万
-$20,347/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$558万
-$20,747/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$749万
-$19,766/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J19" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$598万
-$18,690/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K19" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$502万
-$18,668/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L19" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$504万
-$18,525/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M19" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$526万
-$19,339/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N19" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$526万
-$19,339/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O19" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$520万
-$19,394/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P19" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$707万
-$19,270/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$916万
-$19,699/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$667万
-$19,114/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$669万
-$19,167/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$639万
-$18,309/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$650万
-$18,561/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G20" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$547万
-$20,347/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$530万
-$19,694/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I20" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$789万
-$20,823/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J20" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$640万
-$20,011/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="K20" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$502万
-$18,668/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L20" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$504万
-$18,525/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="M20" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$526万
-$19,339/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N20" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$532万
-$19,546/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O20" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$520万
-$19,394/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P20" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$726万
-$19,793/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$862万
-$18,542/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$659万
-$18,882/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$661万
-$18,935/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$631万
-$18,088/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$635万
-$18,139/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G21" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$533万
-$19,824/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H21" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$524万
-$19,465/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$740万
-$19,529/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J21" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$627万
-$19,585/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K21" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$499万
-$18,554/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L21" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$501万
-$18,413/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M21" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$513万
-$18,848/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$551万
-$20,250/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O21" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$522万
-$19,482/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P21" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$721万
-$19,657/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$900万
-$19,347/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$655万
-$18,766/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$664万
-$19,023/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$627万
-$17,977/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$631万
-$18,028/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G22" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$527万
-$19,600/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$548万
-$20,384/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$743万
-$19,616/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$599万
-$18,722/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K22" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$498万
-$18,498/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L22" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$499万
-$18,357/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M22" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$517万
-$18,990/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N22" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$521万
-$19,164/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O22" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$515万
-$19,216/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P22" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$694万
-$18,921/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$894万
-$19,231/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$672万
-$19,258/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$646万
-$18,500/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$624万
-$17,866/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$662万
-$18,913/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G23" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$524万
-$19,486/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H23" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$523万
-$19,441/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I23" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$731万
-$19,289/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J23" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$574万
-$17,949/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K23" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$519万
-$19,304/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L23" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$469万
-$17,232/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M23" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$506万
-$18,617/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N23" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$516万
-$18,989/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O23" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$510万
-$19,035/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P23" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$728万
-$19,828/呎
-(26年-03月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$889万
-$19,114/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$668万
-$19,139/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$634万
-$18,162/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$620万
-$17,755/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$665万
-$18,994/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G24" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$521万
-$19,367/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H24" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$514万
-$19,120/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I24" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$734万
-$19,374/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J24" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$585万
-$18,291/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K24" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$491万
-$18,269/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L24" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$467万
-$17,179/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="M24" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$505万
-$18,559/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N24" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$518万
-$19,031/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O24" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$509万
-$18,975/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P24" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$671万
-$18,284/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$832万
-$17,886/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$625万
-$17,905/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$661万
-$18,926/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$646万
-$18,510/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$650万
-$18,563/呎
-(25年-09月)</t>
-        </is>
-      </c>
-      <c r="G25" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$515万
-$19,134/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$508万
-$18,891/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="I25" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$756万
-$19,944/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J25" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$571万
-$17,840/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="K25" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$492万
-$18,307/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L25" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$492万
-$18,078/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M25" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$503万
-$18,500/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N25" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$519万
-$19,070/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O25" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$507万
-$18,916/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P25" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$667万
-$18,172/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$816万
-$17,555/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$613万
-$17,564/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$648万
-$18,567/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$634万
-$18,159/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$638万
-$18,215/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$505万
-$18,787/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$488万
-$18,150/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="I26" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$708万
-$18,671/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J26" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$582万
-$18,178/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K26" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$488万
-$18,154/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L26" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$490万
-$18,018/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M26" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$502万
-$18,446/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N26" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$512万
-$18,810/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O26" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$506万
-$18,892/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P26" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$663万
-$18,056/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$818万
-$17,582/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$621万
-$17,781/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$621万
-$17,807/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$595万
-$17,038/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$631万
-$18,039/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G27" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$501万
-$18,609/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$492万
-$18,278/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="I27" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$734万
-$19,378/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J27" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$567万
-$17,727/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K27" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$487万
-$18,095/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L27" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$465万
-$17,112/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="M27" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$500万
-$18,387/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N27" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$510万
-$18,751/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O27" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$505万
-$18,832/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P27" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$656万
-$17,887/呎
-(25年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$796万
-$17,122/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$621万
-$17,781/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$662万
-$18,968/呎
-(26年-01月)</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$595万
-$17,038/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F28" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$598万
-$17,090/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G28" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$501万
-$18,609/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$486万
-$18,082/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="I28" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$705万
-$18,591/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="J28" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$580万
-$18,121/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K28" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$487万
-$18,095/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L28" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$463万
-$17,017/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M28" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$500万
-$18,387/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N28" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$510万
-$18,751/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O28" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$532万
-$19,840/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P28" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$671万
-$18,284/呎
-(26年-02月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$772万
-$16,610/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$615万
-$17,622/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$609万
-$17,459/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$622万
-$17,819/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F29" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$626万
-$17,878/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G29" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$491万
-$18,262/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H29" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$498万
-$18,514/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I29" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$658万
-$17,361/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J29" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$576万
-$18,006/呎
-(26年-02月)</t>
-        </is>
-      </c>
-      <c r="K29" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$484万
-$17,980/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L29" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$491万
-$18,039/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M29" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$497万
-$18,270/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N29" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$516万
-$18,982/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O29" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$502万
-$18,714/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P29" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$694万
-$18,914/呎
-(25年-12月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$765万
-$16,450/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$589万
-$16,883/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$623万
-$17,848/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$577万
-$16,540/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F30" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$613万
-$17,518/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="G30" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$492万
-$18,281/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H30" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$462万
-$17,190/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I30" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$655万
-$17,283/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="J30" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$591万
-$18,478/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="K30" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$482万
-$17,925/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L30" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$484万
-$17,795/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M30" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$522万
-$19,189/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N30" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$507万
-$18,628/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O30" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$500万
-$18,654/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="P30" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$645万
-$17,570/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>A | 465呎 (3房)
-$755万
-$16,233/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>B | 349呎 (2房)
-$613万
-$17,563/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>C | 349呎 (2房)
-$582万
-$16,682/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="inlineStr">
-        <is>
-          <t>D | 349呎 (2房)
-$569万
-$16,298/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="F31" s="17" t="inlineStr">
-        <is>
-          <t>E | 350呎 (2房)
-$573万
-$16,375/呎
-(25年-11月)</t>
-        </is>
-      </c>
-      <c r="G31" s="17" t="inlineStr">
-        <is>
-          <t>F | 269呎 (1房)
-$487万
-$18,102/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="H31" s="17" t="inlineStr">
-        <is>
-          <t>G | 269呎 (1房)
-$482万
-$17,905/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="I31" s="17" t="inlineStr">
-        <is>
-          <t>H | 379呎 (2房)
-$693万
-$18,276/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="J31" s="17" t="inlineStr">
-        <is>
-          <t>J | 320呎 (2房)
-$557万
-$17,392/呎
-(25年-12月)</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>K | 269呎 (1房)
-$480万
-$17,848/呎
-(26年-03月)</t>
-        </is>
-      </c>
-      <c r="L31" s="17" t="inlineStr">
-        <is>
-          <t>L | 272呎 (1房)
-$482万
-$17,708/呎
-(25年-10月)</t>
-        </is>
-      </c>
-      <c r="M31" s="17" t="inlineStr">
-        <is>
-          <t>M | 272呎 (1房)
-$494万
-$18,157/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="N31" s="17" t="inlineStr">
-        <is>
-          <t>N | 272呎 (1房)
-$505万
-$18,573/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="O31" s="17" t="inlineStr">
-        <is>
-          <t>P | 268呎 (1房)
-$499万
-$18,613/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="P31" s="17" t="inlineStr">
-        <is>
-          <t>Q | 367呎 (2房)
-$632万
-$17,208/呎
-(25年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="65" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>A | 428呎 (3房)
-$907万
-$21,200/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>B | 312呎 (2房)
-$657万
-$21,051/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>C | 312呎 (2房)
-$697万
-$22,330/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="inlineStr">
-        <is>
-          <t>D | 312呎 (2房)
-$669万
-$21,436/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="F32" s="17" t="inlineStr">
-        <is>
-          <t>E | 312呎 (2房)
-$676万
-$21,672/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="G32" s="17" t="inlineStr">
-        <is>
-          <t>F | 232呎 (1房)
-$536万
-$23,100/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
-        <is>
-          <t>G | 231呎 (1房)
-$541万
-$23,400/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="I32" s="17" t="inlineStr">
-        <is>
-          <t>H | 343呎 (2房)
-$909万
-$26,500/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="J32" s="17" t="inlineStr">
-        <is>
-          <t>J | 536呎 (3房)
-$1,608万
-$30,000/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="K32" s="17" t="inlineStr">
-        <is>
-          <t>K | 235呎 (1房)
-$790万
-$33,638/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L32" s="17" t="inlineStr">
-        <is>
-          <t>L | 235呎 (1房)
-$689万
-$29,300/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M32" s="17" t="inlineStr">
-        <is>
-          <t>M | 234呎 (1房)
-$716万
-$30,603/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="N32" s="17" t="inlineStr">
-        <is>
-          <t>N | 230呎 (1房)
-$639万
-$27,775/呎
-(26年-05月)</t>
-        </is>
-      </c>
-      <c r="O32" s="17" t="inlineStr">
-        <is>
-          <t>P | 328呎 (2房)
-$827万
-$25,200/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="P32" s="19" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -18995,4 +19174,3594 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 832呎 (4+房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>B | 348呎 (2房)
+$814万
+$23,388/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$818万
+$23,439/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>D | 350呎 (2房)
+$822万
+$23,490/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>E | 269呎 (1房)
+$632万
+$23,507/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$634万
+$23,552/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>G | 379呎 (2房)
+$962万
+$25,377/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 320呎 (2房)
+$712万
+$22,259/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t>J | 269呎 (1房)
+$589万
+$21,894/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>K | 272呎 (1房)
+$596万
+$21,928/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$598万
+$22,000/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>M | 271呎 (1房)
+$593万
+$21,881/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N5" s="23" t="inlineStr"/>
+      <c r="O5" s="23" t="inlineStr"/>
+      <c r="P5" s="23" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$1003万
+$21,571/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$825万
+$23,632/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$785万
+$22,488/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$712万
+$20,409/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$744万
+$21,246/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$596万
+$22,162/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$588万
+$21,873/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$865万
+$22,815/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J6" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$662万
+$20,672/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K6" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$547万
+$20,333/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$531万
+$19,516/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$561万
+$20,632/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N6" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$572万
+$21,044/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$566万
+$21,121/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$807万
+$21,981/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$924万
+$19,879/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$749万
+$21,457/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$725万
+$20,776/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$697万
+$19,958/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$712万
+$20,332/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$571万
+$21,230/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$564万
+$20,956/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$808万
+$21,306/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$632万
+$19,746/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$550万
+$20,454/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L7" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$510万
+$18,748/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$536万
+$19,710/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$547万
+$20,102/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$541万
+$20,169/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$779万
+$21,233/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$929万
+$19,989/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$745万
+$21,334/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$721万
+$20,658/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$693万
+$19,844/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$745万
+$21,298/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$598万
+$22,245/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$552万
+$20,507/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$803万
+$21,184/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$630万
+$19,690/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K8" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$523万
+$19,460/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L8" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$522万
+$19,199/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$563万
+$20,703/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N8" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$545万
+$20,044/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O8" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$539万
+$20,109/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$769万
+$20,947/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$940万
+$20,207/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$740万
+$21,213/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$717万
+$20,540/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$689万
+$19,731/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$704万
+$20,102/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$565万
+$20,997/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$540万
+$20,061/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$760万
+$20,061/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J9" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$628万
+$19,632/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K9" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$519万
+$19,301/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$493万
+$18,136/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$539万
+$19,807/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N9" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$573万
+$21,054/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O9" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$543万
+$20,265/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$767万
+$20,886/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$914万
+$19,657/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$740万
+$21,213/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$717万
+$20,540/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$711万
+$20,374/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$704万
+$20,102/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$565万
+$20,997/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$558万
+$20,726/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$790万
+$20,841/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$628万
+$19,632/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$519万
+$19,301/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$493万
+$18,136/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$533万
+$19,597/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$544万
+$19,985/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$540万
+$20,157/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$808万
+$22,003/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$909万
+$19,544/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$732万
+$20,966/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$709万
+$20,305/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$703万
+$20,143/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$703万
+$20,085/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$588万
+$21,875/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$551万
+$20,497/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$781万
+$20,602/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$624万
+$19,515/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K11" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$516万
+$19,187/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$529万
+$19,432/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$536万
+$19,689/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N11" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$540万
+$19,869/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O11" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$534万
+$19,931/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$803万
+$21,874/呎
+(26年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$899万
+$19,326/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$713万
+$20,439/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$715万
+$20,492/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$699万
+$20,026/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$688万
+$19,652/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$555万
+$20,650/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$548万
+$20,382/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$804万
+$21,206/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$626万
+$19,561/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="K12" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$515万
+$19,128/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L12" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$511万
+$18,776/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$534万
+$19,629/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$568万
+$20,869/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O12" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$533万
+$19,872/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$760万
+$20,702/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$933万
+$20,069/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$709万
+$20,318/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$711万
+$20,374/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$658万
+$18,861/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$662万
+$18,908/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$552万
+$20,532/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$551万
+$20,484/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$799万
+$21,083/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$619万
+$19,343/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K13" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$511万
+$19,013/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$489万
+$17,967/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$525万
+$19,308/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$536万
+$19,693/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O13" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$532万
+$19,856/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$758万
+$20,641/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$933万
+$20,058/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$705万
+$20,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$707万
+$20,254/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$654万
+$18,750/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$658万
+$18,800/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$549万
+$20,417/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$542万
+$20,153/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$794万
+$20,960/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J14" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$655万
+$20,460/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K14" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$508万
+$18,898/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$488万
+$17,959/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$528万
+$19,397/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$561万
+$20,619/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O14" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$526万
+$19,631/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P14" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$741万
+$20,180/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$883万
+$18,993/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$727万
+$20,837/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$700万
+$20,045/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$687万
+$19,675/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$654万
+$18,689/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$557万
+$20,702/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$539万
+$20,038/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$790万
+$20,836/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$646万
+$20,192/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K15" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$507万
+$18,842/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$482万
+$17,709/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$531万
+$19,514/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$531万
+$19,514/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O15" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$525万
+$19,572/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P15" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$742万
+$20,226/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$878万
+$18,883/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$686万
+$19,662/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$688万
+$19,715/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$647万
+$18,529/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$650万
+$18,579/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$554万
+$20,584/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$536万
+$19,923/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$785万
+$20,713/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J16" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$595万
+$18,601/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K16" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$505万
+$18,783/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$486万
+$17,852/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$529万
+$19,456/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N16" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$558万
+$20,497/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O16" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$523万
+$19,513/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P16" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$736万
+$20,060/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$850万
+$18,283/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$682万
+$19,544/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$691万
+$19,807/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$678万
+$19,441/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$646万
+$18,468/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$551万
+$20,465/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$533万
+$19,809/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$725万
+$19,142/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$600万
+$18,748/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K17" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$504万
+$18,728/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$505万
+$18,581/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$528万
+$19,398/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N17" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$528万
+$19,398/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O17" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$521万
+$19,453/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P17" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$734万
+$19,999/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$916万
+$19,699/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$678万
+$19,426/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$680万
+$19,479/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$646万
+$18,513/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$678万
+$19,377/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$547万
+$20,347/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$558万
+$20,747/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$749万
+$19,766/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$598万
+$18,690/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K18" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$502万
+$18,668/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$504万
+$18,525/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$526万
+$19,339/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N18" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$526万
+$19,339/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O18" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$520万
+$19,394/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P18" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$707万
+$19,270/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$916万
+$19,699/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$667万
+$19,114/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$669万
+$19,167/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$639万
+$18,309/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$650万
+$18,561/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$547万
+$20,347/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$530万
+$19,694/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$789万
+$20,823/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J19" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$640万
+$20,011/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="K19" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$502万
+$18,668/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$504万
+$18,525/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$526万
+$19,339/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N19" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$532万
+$19,546/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O19" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$520万
+$19,394/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P19" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$726万
+$19,793/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$862万
+$18,542/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$659万
+$18,882/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$661万
+$18,935/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$631万
+$18,088/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$635万
+$18,139/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$533万
+$19,824/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$524万
+$19,465/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$740万
+$19,529/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J20" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$627万
+$19,585/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K20" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$499万
+$18,554/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$501万
+$18,413/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$513万
+$18,848/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N20" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$551万
+$20,250/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O20" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$522万
+$19,482/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P20" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$721万
+$19,657/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$900万
+$19,347/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$655万
+$18,766/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$664万
+$19,023/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$627万
+$17,977/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$631万
+$18,028/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$527万
+$19,600/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$548万
+$20,384/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$743万
+$19,616/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$599万
+$18,722/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$498万
+$18,498/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$499万
+$18,357/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$517万
+$18,990/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$521万
+$19,164/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$515万
+$19,216/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P21" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$694万
+$18,921/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$894万
+$19,231/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$672万
+$19,258/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$646万
+$18,500/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$624万
+$17,866/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$662万
+$18,913/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$524万
+$19,486/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$523万
+$19,441/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$731万
+$19,289/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$574万
+$17,949/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$519万
+$19,304/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$469万
+$17,232/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$506万
+$18,617/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$516万
+$18,989/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$510万
+$19,035/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$728万
+$19,828/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$889万
+$19,114/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$668万
+$19,139/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$634万
+$18,162/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$620万
+$17,755/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$665万
+$18,994/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$521万
+$19,367/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$514万
+$19,120/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$734万
+$19,374/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$585万
+$18,291/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$491万
+$18,269/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$467万
+$17,179/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$505万
+$18,559/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$518万
+$19,031/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$509万
+$18,975/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$671万
+$18,284/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$832万
+$17,886/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$625万
+$17,905/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$661万
+$18,926/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$646万
+$18,510/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$650万
+$18,563/呎
+(25年-09月)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$515万
+$19,134/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$508万
+$18,891/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$756万
+$19,944/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$571万
+$17,840/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$492万
+$18,307/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$492万
+$18,078/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$503万
+$18,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$519万
+$19,070/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$507万
+$18,916/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$667万
+$18,172/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$816万
+$17,555/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$613万
+$17,564/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$648万
+$18,567/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$634万
+$18,159/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$638万
+$18,215/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$505万
+$18,787/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$488万
+$18,150/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$708万
+$18,671/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$582万
+$18,178/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$488万
+$18,154/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$490万
+$18,018/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$502万
+$18,446/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$512万
+$18,810/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$506万
+$18,892/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P25" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$663万
+$18,056/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$818万
+$17,582/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$621万
+$17,781/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$621万
+$17,807/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$595万
+$17,038/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$631万
+$18,039/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$501万
+$18,609/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$492万
+$18,278/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$734万
+$19,378/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$567万
+$17,727/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$487万
+$18,095/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$465万
+$17,112/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$500万
+$18,387/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$510万
+$18,751/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$505万
+$18,832/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P26" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$656万
+$17,887/呎
+(25年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$796万
+$17,122/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$621万
+$17,781/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$662万
+$18,968/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$595万
+$17,038/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$598万
+$17,090/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$501万
+$18,609/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$486万
+$18,082/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$705万
+$18,591/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="J27" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$580万
+$18,121/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K27" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$487万
+$18,095/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$463万
+$17,017/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$500万
+$18,387/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N27" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$510万
+$18,751/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O27" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$532万
+$19,840/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P27" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$671万
+$18,284/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$772万
+$16,610/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$615万
+$17,622/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D28" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$609万
+$17,459/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$622万
+$17,819/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$626万
+$17,878/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$491万
+$18,262/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$498万
+$18,514/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$658万
+$17,361/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J28" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$576万
+$18,006/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="K28" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$484万
+$17,980/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L28" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$491万
+$18,039/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$497万
+$18,270/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N28" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$516万
+$18,982/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$502万
+$18,714/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P28" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$694万
+$18,914/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$765万
+$16,450/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$589万
+$16,883/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D29" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$623万
+$17,848/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$577万
+$16,540/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$613万
+$17,518/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$492万
+$18,281/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$462万
+$17,190/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$655万
+$17,283/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$591万
+$18,478/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K29" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$482万
+$17,925/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$484万
+$17,795/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$522万
+$19,189/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$507万
+$18,628/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O29" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$500万
+$18,654/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="P29" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$645万
+$17,570/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 465呎 (3房)
+$755万
+$16,233/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 349呎 (2房)
+$613万
+$17,563/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 349呎 (2房)
+$582万
+$16,682/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 349呎 (2房)
+$569万
+$16,298/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 350呎 (2房)
+$573万
+$16,375/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 269呎 (1房)
+$487万
+$18,102/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 269呎 (1房)
+$482万
+$17,905/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 379呎 (2房)
+$693万
+$18,276/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="J30" s="21" t="inlineStr">
+        <is>
+          <t>J | 320呎 (2房)
+$557万
+$17,392/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="K30" s="21" t="inlineStr">
+        <is>
+          <t>K | 269呎 (1房)
+$480万
+$17,848/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="L30" s="21" t="inlineStr">
+        <is>
+          <t>L | 272呎 (1房)
+$482万
+$17,708/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>M | 272呎 (1房)
+$494万
+$18,157/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="N30" s="21" t="inlineStr">
+        <is>
+          <t>N | 272呎 (1房)
+$505万
+$18,573/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t>P | 268呎 (1房)
+$499万
+$18,613/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="P30" s="21" t="inlineStr">
+        <is>
+          <t>Q | 367呎 (2房)
+$632万
+$17,208/呎
+(25年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>A | 428呎 (3房)
+$907万
+$21,200/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>B | 312呎 (2房)
+$657万
+$21,051/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 312呎 (2房)
+$697万
+$22,330/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 312呎 (2房)
+$669万
+$21,436/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 312呎 (2房)
+$676万
+$21,672/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 232呎 (1房)
+$536万
+$23,100/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>G | 231呎 (1房)
+$541万
+$23,400/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
+        <is>
+          <t>H | 343呎 (2房)
+$909万
+$26,500/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="inlineStr">
+        <is>
+          <t>J | 536呎 (3房)
+$1608万
+$30,000/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="K31" s="21" t="inlineStr">
+        <is>
+          <t>K | 235呎 (1房)
+$790万
+$33,638/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>L | 235呎 (1房)
+$689万
+$29,300/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>M | 234呎 (1房)
+$716万
+$30,603/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>N | 230呎 (1房)
+$639万
+$27,775/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="O31" s="21" t="inlineStr">
+        <is>
+          <t>P | 328呎 (2房)
+$827万
+$25,200/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="P31" s="23" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -22046,14 +22046,14 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
-        <v>5015300</v>
+        <v>5068900</v>
       </c>
       <c r="I346" s="5" t="n">
-        <v>18714</v>
+        <v>18914</v>
       </c>
       <c r="J346" s="3" t="inlineStr">
         <is>
@@ -22061,10 +22061,10 @@
         </is>
       </c>
       <c r="K346" s="5" t="n">
-        <v>5015300</v>
+        <v>5068900</v>
       </c>
       <c r="L346" s="5" t="n">
-        <v>18714</v>
+        <v>18914</v>
       </c>
       <c r="M346" s="3" t="inlineStr">
         <is>
@@ -22976,14 +22976,14 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
-        <v>4999400</v>
+        <v>5052900</v>
       </c>
       <c r="I361" s="5" t="n">
-        <v>18654</v>
+        <v>18854</v>
       </c>
       <c r="J361" s="3" t="inlineStr">
         <is>
@@ -22991,10 +22991,10 @@
         </is>
       </c>
       <c r="K361" s="5" t="n">
-        <v>4999400</v>
+        <v>5052900</v>
       </c>
       <c r="L361" s="5" t="n">
-        <v>18654</v>
+        <v>18854</v>
       </c>
       <c r="M361" s="3" t="inlineStr">
         <is>
@@ -28813,9 +28813,9 @@
       <c r="O28" s="21" t="inlineStr">
         <is>
           <t>P | 268呎 (1房)
-$502万
-$18,714/呎
-(26年-05月-11日)</t>
+$507万
+$18,914/呎
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="P28" s="21" t="inlineStr">
@@ -28940,9 +28940,9 @@
       <c r="O29" s="21" t="inlineStr">
         <is>
           <t>P | 268呎 (1房)
-$500万
-$18,654/呎
-(26年-05月-11日)</t>
+$505万
+$18,854/呎
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="P29" s="21" t="inlineStr">

--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="K8" s="5" t="n">
@@ -25819,7 +25819,7 @@
           <t>B | 348呎 (2房)
 $814万
 $23,388/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -25827,7 +25827,7 @@
           <t>C | 349呎 (2房)
 $818万
 $23,439/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -25835,7 +25835,7 @@
           <t>D | 350呎 (2房)
 $822万
 $23,490/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -25843,7 +25843,7 @@
           <t>E | 269呎 (1房)
 $632万
 $23,507/呎
-(26年-06月-29日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -25851,7 +25851,7 @@
           <t>F | 269呎 (1房)
 $634万
 $23,552/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -25867,7 +25867,7 @@
           <t>H | 320呎 (2房)
 $712万
 $22,259/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -25875,7 +25875,7 @@
           <t>J | 269呎 (1房)
 $589万
 $21,894/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -25883,7 +25883,7 @@
           <t>K | 272呎 (1房)
 $596万
 $21,928/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -25891,7 +25891,7 @@
           <t>L | 272呎 (1房)
 $598万
 $22,000/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
@@ -25899,7 +25899,7 @@
           <t>M | 271呎 (1房)
 $593万
 $21,881/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr"/>
@@ -25917,7 +25917,7 @@
           <t>A | 465呎 (3房)
 $1003万
 $21,571/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>B | 349呎 (2房)
 $825万
 $23,632/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -25933,7 +25933,7 @@
           <t>C | 349呎 (2房)
 $785万
 $22,488/呎
-(26年-05月-26日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -25941,7 +25941,7 @@
           <t>D | 349呎 (2房)
 $712万
 $20,409/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -25949,7 +25949,7 @@
           <t>E | 350呎 (2房)
 $744万
 $21,246/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -25957,7 +25957,7 @@
           <t>F | 269呎 (1房)
 $596万
 $22,162/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -25965,7 +25965,7 @@
           <t>G | 269呎 (1房)
 $588万
 $21,873/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -25973,7 +25973,7 @@
           <t>H | 379呎 (2房)
 $865万
 $22,815/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -25981,7 +25981,7 @@
           <t>J | 320呎 (2房)
 $662万
 $20,672/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -25989,7 +25989,7 @@
           <t>K | 269呎 (1房)
 $547万
 $20,333/呎
-(26年-03月-13日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -25997,7 +25997,7 @@
           <t>L | 272呎 (1房)
 $531万
 $19,516/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -26005,7 +26005,7 @@
           <t>M | 272呎 (1房)
 $561万
 $20,632/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -26013,7 +26013,7 @@
           <t>N | 272呎 (1房)
 $572万
 $21,044/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -26021,7 +26021,7 @@
           <t>P | 268呎 (1房)
 $566万
 $21,121/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -26029,7 +26029,7 @@
           <t>Q | 367呎 (2房)
 $807万
 $21,981/呎
-(26年-05月-20日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
           <t>A | 465呎 (3房)
 $924万
 $19,879/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -26052,7 +26052,7 @@
           <t>B | 349呎 (2房)
 $749万
 $21,457/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -26060,7 +26060,7 @@
           <t>C | 349呎 (2房)
 $725万
 $20,776/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -26068,7 +26068,7 @@
           <t>D | 349呎 (2房)
 $697万
 $19,958/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -26076,7 +26076,7 @@
           <t>E | 350呎 (2房)
 $712万
 $20,332/呎
-(26年-03月-20日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -26084,7 +26084,7 @@
           <t>F | 269呎 (1房)
 $571万
 $21,230/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -26092,7 +26092,7 @@
           <t>G | 269呎 (1房)
 $564万
 $20,956/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -26100,7 +26100,7 @@
           <t>H | 379呎 (2房)
 $808万
 $21,306/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -26108,7 +26108,7 @@
           <t>J | 320呎 (2房)
 $632万
 $19,746/呎
-(26年-02月-28日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -26116,7 +26116,7 @@
           <t>K | 269呎 (1房)
 $550万
 $20,454/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -26124,7 +26124,7 @@
           <t>L | 272呎 (1房)
 $510万
 $18,748/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -26132,7 +26132,7 @@
           <t>M | 272呎 (1房)
 $536万
 $19,710/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -26140,7 +26140,7 @@
           <t>N | 272呎 (1房)
 $547万
 $20,102/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -26148,7 +26148,7 @@
           <t>P | 268呎 (1房)
 $541万
 $20,169/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
@@ -26156,7 +26156,7 @@
           <t>Q | 367呎 (2房)
 $779万
 $21,233/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -26171,7 +26171,7 @@
           <t>A | 465呎 (3房)
 $929万
 $19,989/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -26179,7 +26179,7 @@
           <t>B | 349呎 (2房)
 $745万
 $21,334/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -26187,7 +26187,7 @@
           <t>C | 349呎 (2房)
 $721万
 $20,658/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -26195,7 +26195,7 @@
           <t>D | 349呎 (2房)
 $693万
 $19,844/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -26203,7 +26203,7 @@
           <t>E | 350呎 (2房)
 $745万
 $21,298/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -26211,7 +26211,7 @@
           <t>F | 269呎 (1房)
 $598万
 $22,245/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -26219,7 +26219,7 @@
           <t>G | 269呎 (1房)
 $552万
 $20,507/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -26227,7 +26227,7 @@
           <t>H | 379呎 (2房)
 $803万
 $21,184/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -26235,7 +26235,7 @@
           <t>J | 320呎 (2房)
 $630万
 $19,690/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -26243,7 +26243,7 @@
           <t>K | 269呎 (1房)
 $523万
 $19,460/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -26251,7 +26251,7 @@
           <t>L | 272呎 (1房)
 $522万
 $19,199/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -26259,7 +26259,7 @@
           <t>M | 272呎 (1房)
 $563万
 $20,703/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -26267,7 +26267,7 @@
           <t>N | 272呎 (1房)
 $545万
 $20,044/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O8" s="21" t="inlineStr">
@@ -26275,7 +26275,7 @@
           <t>P | 268呎 (1房)
 $539万
 $20,109/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -26283,7 +26283,7 @@
           <t>Q | 367呎 (2房)
 $769万
 $20,947/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -26298,7 +26298,7 @@
           <t>A | 465呎 (3房)
 $940万
 $20,207/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -26306,7 +26306,7 @@
           <t>B | 349呎 (2房)
 $740万
 $21,213/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -26314,7 +26314,7 @@
           <t>C | 349呎 (2房)
 $717万
 $20,540/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -26322,7 +26322,7 @@
           <t>D | 349呎 (2房)
 $689万
 $19,731/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -26330,7 +26330,7 @@
           <t>E | 350呎 (2房)
 $704万
 $20,102/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -26338,7 +26338,7 @@
           <t>F | 269呎 (1房)
 $565万
 $20,997/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -26346,7 +26346,7 @@
           <t>G | 269呎 (1房)
 $540万
 $20,061/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -26354,7 +26354,7 @@
           <t>H | 379呎 (2房)
 $760万
 $20,061/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -26362,7 +26362,7 @@
           <t>J | 320呎 (2房)
 $628万
 $19,632/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -26370,7 +26370,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,301/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -26378,7 +26378,7 @@
           <t>L | 272呎 (1房)
 $493万
 $18,136/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -26386,7 +26386,7 @@
           <t>M | 272呎 (1房)
 $539万
 $19,807/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -26394,7 +26394,7 @@
           <t>N | 272呎 (1房)
 $573万
 $21,054/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -26402,7 +26402,7 @@
           <t>P | 268呎 (1房)
 $543万
 $20,265/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -26410,7 +26410,7 @@
           <t>Q | 367呎 (2房)
 $767万
 $20,886/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -26425,7 +26425,7 @@
           <t>A | 465呎 (3房)
 $914万
 $19,657/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -26433,7 +26433,7 @@
           <t>B | 349呎 (2房)
 $740万
 $21,213/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -26441,7 +26441,7 @@
           <t>C | 349呎 (2房)
 $717万
 $20,540/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -26449,7 +26449,7 @@
           <t>D | 349呎 (2房)
 $711万
 $20,374/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -26457,7 +26457,7 @@
           <t>E | 350呎 (2房)
 $704万
 $20,102/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -26465,7 +26465,7 @@
           <t>F | 269呎 (1房)
 $565万
 $20,997/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -26473,7 +26473,7 @@
           <t>G | 269呎 (1房)
 $558万
 $20,726/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -26481,7 +26481,7 @@
           <t>H | 379呎 (2房)
 $790万
 $20,841/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -26489,7 +26489,7 @@
           <t>J | 320呎 (2房)
 $628万
 $19,632/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -26497,7 +26497,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,301/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -26505,7 +26505,7 @@
           <t>L | 272呎 (1房)
 $493万
 $18,136/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -26513,7 +26513,7 @@
           <t>M | 272呎 (1房)
 $533万
 $19,597/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -26521,7 +26521,7 @@
           <t>N | 272呎 (1房)
 $544万
 $19,985/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>P | 268呎 (1房)
 $540万
 $20,157/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -26537,7 +26537,7 @@
           <t>Q | 367呎 (2房)
 $808万
 $22,003/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -26552,7 +26552,7 @@
           <t>A | 465呎 (3房)
 $909万
 $19,544/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -26560,7 +26560,7 @@
           <t>B | 349呎 (2房)
 $732万
 $20,966/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -26568,7 +26568,7 @@
           <t>C | 349呎 (2房)
 $709万
 $20,305/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -26576,7 +26576,7 @@
           <t>D | 349呎 (2房)
 $703万
 $20,143/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>E | 350呎 (2房)
 $703万
 $20,085/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -26592,7 +26592,7 @@
           <t>F | 269呎 (1房)
 $588万
 $21,875/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -26600,7 +26600,7 @@
           <t>G | 269呎 (1房)
 $551万
 $20,497/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -26608,7 +26608,7 @@
           <t>H | 379呎 (2房)
 $781万
 $20,602/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -26616,7 +26616,7 @@
           <t>J | 320呎 (2房)
 $624万
 $19,515/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -26624,7 +26624,7 @@
           <t>K | 269呎 (1房)
 $516万
 $19,187/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -26632,7 +26632,7 @@
           <t>L | 272呎 (1房)
 $529万
 $19,432/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>M | 272呎 (1房)
 $536万
 $19,689/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>N | 272呎 (1房)
 $540万
 $19,869/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>P | 268呎 (1房)
 $534万
 $19,931/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>Q | 367呎 (2房)
 $803万
 $21,874/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -26679,7 +26679,7 @@
           <t>A | 465呎 (3房)
 $899万
 $19,326/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -26687,7 +26687,7 @@
           <t>B | 349呎 (2房)
 $713万
 $20,439/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -26695,7 +26695,7 @@
           <t>C | 349呎 (2房)
 $715万
 $20,492/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -26703,7 +26703,7 @@
           <t>D | 349呎 (2房)
 $699万
 $20,026/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -26711,7 +26711,7 @@
           <t>E | 350呎 (2房)
 $688万
 $19,652/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -26719,7 +26719,7 @@
           <t>F | 269呎 (1房)
 $555万
 $20,650/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -26727,7 +26727,7 @@
           <t>G | 269呎 (1房)
 $548万
 $20,382/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -26735,7 +26735,7 @@
           <t>H | 379呎 (2房)
 $804万
 $21,206/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -26743,7 +26743,7 @@
           <t>J | 320呎 (2房)
 $626万
 $19,561/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -26751,7 +26751,7 @@
           <t>K | 269呎 (1房)
 $515万
 $19,128/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -26759,7 +26759,7 @@
           <t>L | 272呎 (1房)
 $511万
 $18,776/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -26767,7 +26767,7 @@
           <t>M | 272呎 (1房)
 $534万
 $19,629/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -26775,7 +26775,7 @@
           <t>N | 272呎 (1房)
 $568万
 $20,869/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -26783,7 +26783,7 @@
           <t>P | 268呎 (1房)
 $533万
 $19,872/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -26791,7 +26791,7 @@
           <t>Q | 367呎 (2房)
 $760万
 $20,702/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -26806,7 +26806,7 @@
           <t>A | 465呎 (3房)
 $933万
 $20,069/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -26814,7 +26814,7 @@
           <t>B | 349呎 (2房)
 $709万
 $20,318/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -26822,7 +26822,7 @@
           <t>C | 349呎 (2房)
 $711万
 $20,374/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -26830,7 +26830,7 @@
           <t>D | 349呎 (2房)
 $658万
 $18,861/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -26838,7 +26838,7 @@
           <t>E | 350呎 (2房)
 $662万
 $18,908/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -26846,7 +26846,7 @@
           <t>F | 269呎 (1房)
 $552万
 $20,532/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -26854,7 +26854,7 @@
           <t>G | 269呎 (1房)
 $551万
 $20,484/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -26862,7 +26862,7 @@
           <t>H | 379呎 (2房)
 $799万
 $21,083/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -26870,7 +26870,7 @@
           <t>J | 320呎 (2房)
 $619万
 $19,343/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -26878,7 +26878,7 @@
           <t>K | 269呎 (1房)
 $511万
 $19,013/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -26886,7 +26886,7 @@
           <t>L | 272呎 (1房)
 $489万
 $17,967/呎
-(25年-11月-27日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -26894,7 +26894,7 @@
           <t>M | 272呎 (1房)
 $525万
 $19,308/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -26902,7 +26902,7 @@
           <t>N | 272呎 (1房)
 $536万
 $19,693/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -26910,7 +26910,7 @@
           <t>P | 268呎 (1房)
 $532万
 $19,856/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P13" s="21" t="inlineStr">
@@ -26918,7 +26918,7 @@
           <t>Q | 367呎 (2房)
 $758万
 $20,641/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -26933,7 +26933,7 @@
           <t>A | 465呎 (3房)
 $933万
 $20,058/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -26941,7 +26941,7 @@
           <t>B | 349呎 (2房)
 $705万
 $20,200/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -26949,7 +26949,7 @@
           <t>C | 349呎 (2房)
 $707万
 $20,254/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -26957,7 +26957,7 @@
           <t>D | 349呎 (2房)
 $654万
 $18,750/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -26965,7 +26965,7 @@
           <t>E | 350呎 (2房)
 $658万
 $18,800/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -26973,7 +26973,7 @@
           <t>F | 269呎 (1房)
 $549万
 $20,417/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -26981,7 +26981,7 @@
           <t>G | 269呎 (1房)
 $542万
 $20,153/呎
-(26年-04月-07日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -26989,7 +26989,7 @@
           <t>H | 379呎 (2房)
 $794万
 $20,960/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -26997,7 +26997,7 @@
           <t>J | 320呎 (2房)
 $655万
 $20,460/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -27005,7 +27005,7 @@
           <t>K | 269呎 (1房)
 $508万
 $18,898/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -27013,7 +27013,7 @@
           <t>L | 272呎 (1房)
 $488万
 $17,959/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -27021,7 +27021,7 @@
           <t>M | 272呎 (1房)
 $528万
 $19,397/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -27029,7 +27029,7 @@
           <t>N | 272呎 (1房)
 $561万
 $20,619/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -27037,7 +27037,7 @@
           <t>P | 268呎 (1房)
 $526万
 $19,631/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -27045,7 +27045,7 @@
           <t>Q | 367呎 (2房)
 $741万
 $20,180/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
           <t>A | 465呎 (3房)
 $883万
 $18,993/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>B | 349呎 (2房)
 $727万
 $20,837/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27076,7 +27076,7 @@
           <t>C | 349呎 (2房)
 $700万
 $20,045/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -27084,7 +27084,7 @@
           <t>D | 349呎 (2房)
 $687万
 $19,675/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27092,7 +27092,7 @@
           <t>E | 350呎 (2房)
 $654万
 $18,689/呎
-(25年-09月-13日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -27100,7 +27100,7 @@
           <t>F | 269呎 (1房)
 $557万
 $20,702/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -27108,7 +27108,7 @@
           <t>G | 269呎 (1房)
 $539万
 $20,038/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -27116,7 +27116,7 @@
           <t>H | 379呎 (2房)
 $790万
 $20,836/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -27124,7 +27124,7 @@
           <t>J | 320呎 (2房)
 $646万
 $20,192/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -27132,7 +27132,7 @@
           <t>K | 269呎 (1房)
 $507万
 $18,842/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -27140,7 +27140,7 @@
           <t>L | 272呎 (1房)
 $482万
 $17,709/呎
-(25年-11月-24日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -27148,7 +27148,7 @@
           <t>M | 272呎 (1房)
 $531万
 $19,514/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -27156,7 +27156,7 @@
           <t>N | 272呎 (1房)
 $531万
 $19,514/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -27164,7 +27164,7 @@
           <t>P | 268呎 (1房)
 $525万
 $19,572/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -27172,7 +27172,7 @@
           <t>Q | 367呎 (2房)
 $742万
 $20,226/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -27187,7 +27187,7 @@
           <t>A | 465呎 (3房)
 $878万
 $18,883/呎
-(25年-12月-28日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -27195,7 +27195,7 @@
           <t>B | 349呎 (2房)
 $686万
 $19,662/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -27203,7 +27203,7 @@
           <t>C | 349呎 (2房)
 $688万
 $19,715/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -27211,7 +27211,7 @@
           <t>D | 349呎 (2房)
 $647万
 $18,529/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -27219,7 +27219,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,579/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -27227,7 +27227,7 @@
           <t>F | 269呎 (1房)
 $554万
 $20,584/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -27235,7 +27235,7 @@
           <t>G | 269呎 (1房)
 $536万
 $19,923/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -27243,7 +27243,7 @@
           <t>H | 379呎 (2房)
 $785万
 $20,713/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -27251,7 +27251,7 @@
           <t>J | 320呎 (2房)
 $595万
 $18,601/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -27259,7 +27259,7 @@
           <t>K | 269呎 (1房)
 $505万
 $18,783/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -27267,7 +27267,7 @@
           <t>L | 272呎 (1房)
 $486万
 $17,852/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -27275,7 +27275,7 @@
           <t>M | 272呎 (1房)
 $529万
 $19,456/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -27283,7 +27283,7 @@
           <t>N | 272呎 (1房)
 $558万
 $20,497/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O16" s="21" t="inlineStr">
@@ -27291,7 +27291,7 @@
           <t>P | 268呎 (1房)
 $523万
 $19,513/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P16" s="21" t="inlineStr">
@@ -27299,7 +27299,7 @@
           <t>Q | 367呎 (2房)
 $736万
 $20,060/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
           <t>A | 465呎 (3房)
 $850万
 $18,283/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -27322,7 +27322,7 @@
           <t>B | 349呎 (2房)
 $682万
 $19,544/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27330,7 +27330,7 @@
           <t>C | 349呎 (2房)
 $691万
 $19,807/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -27338,7 +27338,7 @@
           <t>D | 349呎 (2房)
 $678万
 $19,441/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -27346,7 +27346,7 @@
           <t>E | 350呎 (2房)
 $646万
 $18,468/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -27354,7 +27354,7 @@
           <t>F | 269呎 (1房)
 $551万
 $20,465/呎
-(26年-05月-21日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -27362,7 +27362,7 @@
           <t>G | 269呎 (1房)
 $533万
 $19,809/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -27370,7 +27370,7 @@
           <t>H | 379呎 (2房)
 $725万
 $19,142/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -27378,7 +27378,7 @@
           <t>J | 320呎 (2房)
 $600万
 $18,748/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -27386,7 +27386,7 @@
           <t>K | 269呎 (1房)
 $504万
 $18,728/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -27394,7 +27394,7 @@
           <t>L | 272呎 (1房)
 $505万
 $18,581/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -27402,7 +27402,7 @@
           <t>M | 272呎 (1房)
 $528万
 $19,398/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -27410,7 +27410,7 @@
           <t>N | 272呎 (1房)
 $528万
 $19,398/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
@@ -27418,7 +27418,7 @@
           <t>P | 268呎 (1房)
 $521万
 $19,453/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P17" s="21" t="inlineStr">
@@ -27426,7 +27426,7 @@
           <t>Q | 367呎 (2房)
 $734万
 $19,999/呎
-(26年-03月-20日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -27441,7 +27441,7 @@
           <t>A | 465呎 (3房)
 $916万
 $19,699/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -27449,7 +27449,7 @@
           <t>B | 349呎 (2房)
 $678万
 $19,426/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27457,7 +27457,7 @@
           <t>C | 349呎 (2房)
 $680万
 $19,479/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -27465,7 +27465,7 @@
           <t>D | 349呎 (2房)
 $646万
 $18,513/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -27473,7 +27473,7 @@
           <t>E | 350呎 (2房)
 $678万
 $19,377/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -27481,7 +27481,7 @@
           <t>F | 269呎 (1房)
 $547万
 $20,347/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -27489,7 +27489,7 @@
           <t>G | 269呎 (1房)
 $558万
 $20,747/呎
-(26年-03月-12日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -27497,7 +27497,7 @@
           <t>H | 379呎 (2房)
 $749万
 $19,766/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -27505,7 +27505,7 @@
           <t>J | 320呎 (2房)
 $598万
 $18,690/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -27513,7 +27513,7 @@
           <t>K | 269呎 (1房)
 $502万
 $18,668/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -27521,7 +27521,7 @@
           <t>L | 272呎 (1房)
 $504万
 $18,525/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -27529,7 +27529,7 @@
           <t>M | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -27537,7 +27537,7 @@
           <t>N | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -27545,7 +27545,7 @@
           <t>P | 268呎 (1房)
 $520万
 $19,394/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P18" s="21" t="inlineStr">
@@ -27553,7 +27553,7 @@
           <t>Q | 367呎 (2房)
 $707万
 $19,270/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
           <t>A | 465呎 (3房)
 $916万
 $19,699/呎
-(25年-09月-25日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -27576,7 +27576,7 @@
           <t>B | 349呎 (2房)
 $667万
 $19,114/呎
-(26年-01月-11日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -27584,7 +27584,7 @@
           <t>C | 349呎 (2房)
 $669万
 $19,167/呎
-(26年-02月-22日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -27592,7 +27592,7 @@
           <t>D | 349呎 (2房)
 $639万
 $18,309/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -27600,7 +27600,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,561/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -27608,7 +27608,7 @@
           <t>F | 269呎 (1房)
 $547万
 $20,347/呎
-(26年-05月-17日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -27616,7 +27616,7 @@
           <t>G | 269呎 (1房)
 $530万
 $19,694/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -27624,7 +27624,7 @@
           <t>H | 379呎 (2房)
 $789万
 $20,823/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -27632,7 +27632,7 @@
           <t>J | 320呎 (2房)
 $640万
 $20,011/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -27640,7 +27640,7 @@
           <t>K | 269呎 (1房)
 $502万
 $18,668/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -27648,7 +27648,7 @@
           <t>L | 272呎 (1房)
 $504万
 $18,525/呎
-(25年-09月-13日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -27656,7 +27656,7 @@
           <t>M | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -27664,7 +27664,7 @@
           <t>N | 272呎 (1房)
 $532万
 $19,546/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
@@ -27672,7 +27672,7 @@
           <t>P | 268呎 (1房)
 $520万
 $19,394/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P19" s="21" t="inlineStr">
@@ -27680,7 +27680,7 @@
           <t>Q | 367呎 (2房)
 $726万
 $19,793/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -27695,7 +27695,7 @@
           <t>A | 465呎 (3房)
 $862万
 $18,542/呎
-(25年-11月-04日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -27703,7 +27703,7 @@
           <t>B | 349呎 (2房)
 $659万
 $18,882/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -27711,7 +27711,7 @@
           <t>C | 349呎 (2房)
 $661万
 $18,935/呎
-(26年-01月-27日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -27719,7 +27719,7 @@
           <t>D | 349呎 (2房)
 $631万
 $18,088/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -27727,7 +27727,7 @@
           <t>E | 350呎 (2房)
 $635万
 $18,139/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -27735,7 +27735,7 @@
           <t>F | 269呎 (1房)
 $533万
 $19,824/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -27743,7 +27743,7 @@
           <t>G | 269呎 (1房)
 $524万
 $19,465/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -27751,7 +27751,7 @@
           <t>H | 379呎 (2房)
 $740万
 $19,529/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -27759,7 +27759,7 @@
           <t>J | 320呎 (2房)
 $627万
 $19,585/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -27767,7 +27767,7 @@
           <t>K | 269呎 (1房)
 $499万
 $18,554/呎
-(26年-03月-30日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>L | 272呎 (1房)
 $501万
 $18,413/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>M | 272呎 (1房)
 $513万
 $18,848/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -27791,7 +27791,7 @@
           <t>N | 272呎 (1房)
 $551万
 $20,250/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -27799,7 +27799,7 @@
           <t>P | 268呎 (1房)
 $522万
 $19,482/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P20" s="21" t="inlineStr">
@@ -27807,7 +27807,7 @@
           <t>Q | 367呎 (2房)
 $721万
 $19,657/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
           <t>A | 465呎 (3房)
 $900万
 $19,347/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -27830,7 +27830,7 @@
           <t>B | 349呎 (2房)
 $655万
 $18,766/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -27838,7 +27838,7 @@
           <t>C | 349呎 (2房)
 $664万
 $19,023/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27846,7 +27846,7 @@
           <t>D | 349呎 (2房)
 $627万
 $17,977/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -27854,7 +27854,7 @@
           <t>E | 350呎 (2房)
 $631万
 $18,028/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -27862,7 +27862,7 @@
           <t>F | 269呎 (1房)
 $527万
 $19,600/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -27870,7 +27870,7 @@
           <t>G | 269呎 (1房)
 $548万
 $20,384/呎
-(26年-03月-05日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -27878,7 +27878,7 @@
           <t>H | 379呎 (2房)
 $743万
 $19,616/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -27886,7 +27886,7 @@
           <t>J | 320呎 (2房)
 $599万
 $18,722/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -27894,7 +27894,7 @@
           <t>K | 269呎 (1房)
 $498万
 $18,498/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -27902,7 +27902,7 @@
           <t>L | 272呎 (1房)
 $499万
 $18,357/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -27910,7 +27910,7 @@
           <t>M | 272呎 (1房)
 $517万
 $18,990/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -27918,7 +27918,7 @@
           <t>N | 272呎 (1房)
 $521万
 $19,164/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -27926,7 +27926,7 @@
           <t>P | 268呎 (1房)
 $515万
 $19,216/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P21" s="21" t="inlineStr">
@@ -27934,7 +27934,7 @@
           <t>Q | 367呎 (2房)
 $694万
 $18,921/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -27949,7 +27949,7 @@
           <t>A | 465呎 (3房)
 $894万
 $19,231/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -27957,7 +27957,7 @@
           <t>B | 349呎 (2房)
 $672万
 $19,258/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -27965,7 +27965,7 @@
           <t>C | 349呎 (2房)
 $646万
 $18,500/呎
-(25年-11月-09日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27973,7 +27973,7 @@
           <t>D | 349呎 (2房)
 $624万
 $17,866/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -27981,7 +27981,7 @@
           <t>E | 350呎 (2房)
 $662万
 $18,913/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -27989,7 +27989,7 @@
           <t>F | 269呎 (1房)
 $524万
 $19,486/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -27997,7 +27997,7 @@
           <t>G | 269呎 (1房)
 $523万
 $19,441/呎
-(26年-03月-04日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -28005,7 +28005,7 @@
           <t>H | 379呎 (2房)
 $731万
 $19,289/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -28013,7 +28013,7 @@
           <t>J | 320呎 (2房)
 $574万
 $17,949/呎
-(25年-12月-07日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -28021,7 +28021,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,304/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -28029,7 +28029,7 @@
           <t>L | 272呎 (1房)
 $469万
 $17,232/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -28037,7 +28037,7 @@
           <t>M | 272呎 (1房)
 $506万
 $18,617/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -28045,7 +28045,7 @@
           <t>N | 272呎 (1房)
 $516万
 $18,989/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>P | 268呎 (1房)
 $510万
 $19,035/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P22" s="21" t="inlineStr">
@@ -28061,7 +28061,7 @@
           <t>Q | 367呎 (2房)
 $728万
 $19,828/呎
-(26年-03月-01日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -28076,7 +28076,7 @@
           <t>A | 465呎 (3房)
 $889万
 $19,114/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -28084,7 +28084,7 @@
           <t>B | 349呎 (2房)
 $668万
 $19,139/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -28092,7 +28092,7 @@
           <t>C | 349呎 (2房)
 $634万
 $18,162/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -28100,7 +28100,7 @@
           <t>D | 349呎 (2房)
 $620万
 $17,755/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -28108,7 +28108,7 @@
           <t>E | 350呎 (2房)
 $665万
 $18,994/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -28116,7 +28116,7 @@
           <t>F | 269呎 (1房)
 $521万
 $19,367/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -28124,7 +28124,7 @@
           <t>G | 269呎 (1房)
 $514万
 $19,120/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -28132,7 +28132,7 @@
           <t>H | 379呎 (2房)
 $734万
 $19,374/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -28140,7 +28140,7 @@
           <t>J | 320呎 (2房)
 $585万
 $18,291/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -28148,7 +28148,7 @@
           <t>K | 269呎 (1房)
 $491万
 $18,269/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>L | 272呎 (1房)
 $467万
 $17,179/呎
-(25年-09月-28日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>M | 272呎 (1房)
 $505万
 $18,559/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -28172,7 +28172,7 @@
           <t>N | 272呎 (1房)
 $518万
 $19,031/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -28180,7 +28180,7 @@
           <t>P | 268呎 (1房)
 $509万
 $18,975/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P23" s="21" t="inlineStr">
@@ -28188,7 +28188,7 @@
           <t>Q | 367呎 (2房)
 $671万
 $18,284/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -28203,7 +28203,7 @@
           <t>A | 465呎 (3房)
 $832万
 $17,886/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -28211,7 +28211,7 @@
           <t>B | 349呎 (2房)
 $625万
 $17,905/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -28219,7 +28219,7 @@
           <t>C | 349呎 (2房)
 $661万
 $18,926/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -28227,7 +28227,7 @@
           <t>D | 349呎 (2房)
 $646万
 $18,510/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -28235,7 +28235,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,563/呎
-(25年-09月-13日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -28243,7 +28243,7 @@
           <t>F | 269呎 (1房)
 $515万
 $19,134/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -28251,7 +28251,7 @@
           <t>G | 269呎 (1房)
 $508万
 $18,891/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -28259,7 +28259,7 @@
           <t>H | 379呎 (2房)
 $756万
 $19,944/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -28267,7 +28267,7 @@
           <t>J | 320呎 (2房)
 $571万
 $17,840/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -28275,7 +28275,7 @@
           <t>K | 269呎 (1房)
 $492万
 $18,307/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -28283,7 +28283,7 @@
           <t>L | 272呎 (1房)
 $492万
 $18,078/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -28291,7 +28291,7 @@
           <t>M | 272呎 (1房)
 $503万
 $18,500/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -28299,7 +28299,7 @@
           <t>N | 272呎 (1房)
 $519万
 $19,070/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -28307,7 +28307,7 @@
           <t>P | 268呎 (1房)
 $507万
 $18,916/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P24" s="21" t="inlineStr">
@@ -28315,7 +28315,7 @@
           <t>Q | 367呎 (2房)
 $667万
 $18,172/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -28330,7 +28330,7 @@
           <t>A | 465呎 (3房)
 $816万
 $17,555/呎
-(25年-10月-12日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -28338,7 +28338,7 @@
           <t>B | 349呎 (2房)
 $613万
 $17,564/呎
-(25年-12月-04日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -28346,7 +28346,7 @@
           <t>C | 349呎 (2房)
 $648万
 $18,567/呎
-(25年-10月-20日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -28354,7 +28354,7 @@
           <t>D | 349呎 (2房)
 $634万
 $18,159/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -28362,7 +28362,7 @@
           <t>E | 350呎 (2房)
 $638万
 $18,215/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -28370,7 +28370,7 @@
           <t>F | 269呎 (1房)
 $505万
 $18,787/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -28378,7 +28378,7 @@
           <t>G | 269呎 (1房)
 $488万
 $18,150/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -28386,7 +28386,7 @@
           <t>H | 379呎 (2房)
 $708万
 $18,671/呎
-(26年-03月-19日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -28394,7 +28394,7 @@
           <t>J | 320呎 (2房)
 $582万
 $18,178/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -28402,7 +28402,7 @@
           <t>K | 269呎 (1房)
 $488万
 $18,154/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -28410,7 +28410,7 @@
           <t>L | 272呎 (1房)
 $490万
 $18,018/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -28418,7 +28418,7 @@
           <t>M | 272呎 (1房)
 $502万
 $18,446/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -28426,7 +28426,7 @@
           <t>N | 272呎 (1房)
 $512万
 $18,810/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -28434,7 +28434,7 @@
           <t>P | 268呎 (1房)
 $506万
 $18,892/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P25" s="21" t="inlineStr">
@@ -28442,7 +28442,7 @@
           <t>Q | 367呎 (2房)
 $663万
 $18,056/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
           <t>A | 465呎 (3房)
 $818万
 $17,582/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -28465,7 +28465,7 @@
           <t>B | 349呎 (2房)
 $621万
 $17,781/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -28473,7 +28473,7 @@
           <t>C | 349呎 (2房)
 $621万
 $17,807/呎
-(26年-01月-29日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -28481,7 +28481,7 @@
           <t>D | 349呎 (2房)
 $595万
 $17,038/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -28489,7 +28489,7 @@
           <t>E | 350呎 (2房)
 $631万
 $18,039/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -28497,7 +28497,7 @@
           <t>F | 269呎 (1房)
 $501万
 $18,609/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -28505,7 +28505,7 @@
           <t>G | 269呎 (1房)
 $492万
 $18,278/呎
-(26年-01月-12日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -28513,7 +28513,7 @@
           <t>H | 379呎 (2房)
 $734万
 $19,378/呎
-(26年-03月-03日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -28521,7 +28521,7 @@
           <t>J | 320呎 (2房)
 $567万
 $17,727/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -28529,7 +28529,7 @@
           <t>K | 269呎 (1房)
 $487万
 $18,095/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -28537,7 +28537,7 @@
           <t>L | 272呎 (1房)
 $465万
 $17,112/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -28545,7 +28545,7 @@
           <t>M | 272呎 (1房)
 $500万
 $18,387/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -28553,7 +28553,7 @@
           <t>N | 272呎 (1房)
 $510万
 $18,751/呎
-(26年-04月-22日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -28561,7 +28561,7 @@
           <t>P | 268呎 (1房)
 $505万
 $18,832/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="P26" s="21" t="inlineStr">
@@ -28569,7 +28569,7 @@
           <t>Q | 367呎 (2房)
 $656万
 $17,887/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -28584,7 +28584,7 @@
           <t>A | 465呎 (3房)
 $796万
 $17,122/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -28592,7 +28592,7 @@
           <t>B | 349呎 (2房)
 $621万
 $17,781/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -28600,7 +28600,7 @@
           <t>C | 349呎 (2房)
 $662万
 $18,968/呎
-(26年-01月-08日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -28608,7 +28608,7 @@
           <t>D | 349呎 (2房)
 $595万
 $17,038/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -28616,7 +28616,7 @@
           <t>E | 350呎 (2房)
 $598万
 $17,090/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -28624,7 +28624,7 @@
           <t>F | 269呎 (1房)
 $501万
 $18,609/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -28632,7 +28632,7 @@
           <t>G | 269呎 (1房)
 $486万
 $18,082/呎
-(26年-02月-15日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -28640,7 +28640,7 @@
           <t>H | 379呎 (2房)
 $705万
 $18,591/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -28648,7 +28648,7 @@
           <t>J | 320呎 (2房)
 $580万
 $18,121/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -28656,7 +28656,7 @@
           <t>K | 269呎 (1房)
 $487万
 $18,095/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -28664,7 +28664,7 @@
           <t>L | 272呎 (1房)
 $463万
 $17,017/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -28672,7 +28672,7 @@
           <t>M | 272呎 (1房)
 $500万
 $18,387/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -28680,7 +28680,7 @@
           <t>N | 272呎 (1房)
 $510万
 $18,751/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -28688,7 +28688,7 @@
           <t>P | 268呎 (1房)
 $532万
 $19,840/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P27" s="21" t="inlineStr">
@@ -28696,7 +28696,7 @@
           <t>Q | 367呎 (2房)
 $671万
 $18,284/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -28711,7 +28711,7 @@
           <t>A | 465呎 (3房)
 $772万
 $16,610/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -28719,7 +28719,7 @@
           <t>B | 349呎 (2房)
 $615万
 $17,622/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -28727,7 +28727,7 @@
           <t>C | 349呎 (2房)
 $609万
 $17,459/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -28735,7 +28735,7 @@
           <t>D | 349呎 (2房)
 $622万
 $17,819/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -28743,7 +28743,7 @@
           <t>E | 350呎 (2房)
 $626万
 $17,878/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -28751,7 +28751,7 @@
           <t>F | 269呎 (1房)
 $491万
 $18,262/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -28759,7 +28759,7 @@
           <t>G | 269呎 (1房)
 $498万
 $18,514/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -28767,7 +28767,7 @@
           <t>H | 379呎 (2房)
 $658万
 $17,361/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -28775,7 +28775,7 @@
           <t>J | 320呎 (2房)
 $576万
 $18,006/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -28783,7 +28783,7 @@
           <t>K | 269呎 (1房)
 $484万
 $17,980/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -28791,7 +28791,7 @@
           <t>L | 272呎 (1房)
 $491万
 $18,039/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>M | 272呎 (1房)
 $497万
 $18,270/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>N | 272呎 (1房)
 $516万
 $18,982/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -28815,7 +28815,7 @@
           <t>P | 268呎 (1房)
 $507万
 $18,914/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P28" s="21" t="inlineStr">
@@ -28823,7 +28823,7 @@
           <t>Q | 367呎 (2房)
 $694万
 $18,914/呎
-(25年-12月-05日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -28838,7 +28838,7 @@
           <t>A | 465呎 (3房)
 $765万
 $16,450/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -28846,7 +28846,7 @@
           <t>B | 349呎 (2房)
 $589万
 $16,883/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -28854,7 +28854,7 @@
           <t>C | 349呎 (2房)
 $623万
 $17,848/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -28862,7 +28862,7 @@
           <t>D | 349呎 (2房)
 $577万
 $16,540/呎
-(25年-10月-09日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -28870,7 +28870,7 @@
           <t>E | 350呎 (2房)
 $613万
 $17,518/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -28878,7 +28878,7 @@
           <t>F | 269呎 (1房)
 $492万
 $18,281/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -28886,7 +28886,7 @@
           <t>G | 269呎 (1房)
 $462万
 $17,190/呎
-(25年-10月-15日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -28894,7 +28894,7 @@
           <t>H | 379呎 (2房)
 $655万
 $17,283/呎
-(25年-10月-13日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -28902,7 +28902,7 @@
           <t>J | 320呎 (2房)
 $591万
 $18,478/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -28910,7 +28910,7 @@
           <t>K | 269呎 (1房)
 $482万
 $17,925/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -28918,7 +28918,7 @@
           <t>L | 272呎 (1房)
 $484万
 $17,795/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -28926,7 +28926,7 @@
           <t>M | 272呎 (1房)
 $522万
 $19,189/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -28934,7 +28934,7 @@
           <t>N | 272呎 (1房)
 $507万
 $18,628/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
@@ -28942,7 +28942,7 @@
           <t>P | 268呎 (1房)
 $505万
 $18,854/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P29" s="21" t="inlineStr">
@@ -28950,7 +28950,7 @@
           <t>Q | 367呎 (2房)
 $645万
 $17,570/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
           <t>A | 465呎 (3房)
 $755万
 $16,233/呎
-(25年-10月-05日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -28973,7 +28973,7 @@
           <t>B | 349呎 (2房)
 $613万
 $17,563/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -28981,7 +28981,7 @@
           <t>C | 349呎 (2房)
 $582万
 $16,682/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -28989,7 +28989,7 @@
           <t>D | 349呎 (2房)
 $569万
 $16,298/呎
-(25年-10月-08日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -28997,7 +28997,7 @@
           <t>E | 350呎 (2房)
 $573万
 $16,375/呎
-(25年-11月-03日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -29005,7 +29005,7 @@
           <t>F | 269呎 (1房)
 $487万
 $18,102/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -29013,7 +29013,7 @@
           <t>G | 269呎 (1房)
 $482万
 $17,905/呎
-(25年-10月-21日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -29021,7 +29021,7 @@
           <t>H | 379呎 (2房)
 $693万
 $18,276/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -29029,7 +29029,7 @@
           <t>J | 320呎 (2房)
 $557万
 $17,392/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -29037,7 +29037,7 @@
           <t>K | 269呎 (1房)
 $480万
 $17,848/呎
-(26年-03月-25日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -29045,7 +29045,7 @@
           <t>L | 272呎 (1房)
 $482万
 $17,708/呎
-(25年-10月-01日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>M | 272呎 (1房)
 $494万
 $18,157/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>N | 272呎 (1房)
 $505万
 $18,573/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>P | 268呎 (1房)
 $499万
 $18,613/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="P30" s="21" t="inlineStr">
@@ -29077,7 +29077,7 @@
           <t>Q | 367呎 (2房)
 $632万
 $17,208/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
     </row>
@@ -29092,7 +29092,7 @@
           <t>A | 428呎 (3房)
 $907万
 $21,200/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -29100,7 +29100,7 @@
           <t>B | 312呎 (2房)
 $657万
 $21,051/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -29108,7 +29108,7 @@
           <t>C | 312呎 (2房)
 $697万
 $22,330/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -29116,7 +29116,7 @@
           <t>D | 312呎 (2房)
 $669万
 $21,436/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -29124,7 +29124,7 @@
           <t>E | 312呎 (2房)
 $676万
 $21,672/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -29132,7 +29132,7 @@
           <t>F | 232呎 (1房)
 $536万
 $23,100/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -29140,7 +29140,7 @@
           <t>G | 231呎 (1房)
 $541万
 $23,400/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -29148,7 +29148,7 @@
           <t>H | 343呎 (2房)
 $909万
 $26,500/呎
-(26年-04月-29日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -29156,7 +29156,7 @@
           <t>J | 536呎 (3房)
 $1608万
 $30,000/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -29164,7 +29164,7 @@
           <t>K | 235呎 (1房)
 $790万
 $33,638/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -29172,7 +29172,7 @@
           <t>L | 235呎 (1房)
 $689万
 $29,300/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -29180,7 +29180,7 @@
           <t>M | 234呎 (1房)
 $716万
 $30,603/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
@@ -29188,7 +29188,7 @@
           <t>N | 230呎 (1房)
 $639万
 $27,775/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
@@ -29196,7 +29196,7 @@
           <t>P | 328呎 (2房)
 $827万
 $25,200/呎
-(26年-06月-08日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr"/>

--- a/files/九龙-马头角-壹沐第1期.xlsx
+++ b/files/九龙-马头角-壹沐第1期.xlsx
@@ -25819,7 +25819,7 @@
           <t>B | 348呎 (2房)
 $814万
 $23,388/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -25827,7 +25827,7 @@
           <t>C | 349呎 (2房)
 $818万
 $23,439/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -25835,7 +25835,7 @@
           <t>D | 350呎 (2房)
 $822万
 $23,490/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -25843,7 +25843,7 @@
           <t>E | 269呎 (1房)
 $632万
 $23,507/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -25851,7 +25851,7 @@
           <t>F | 269呎 (1房)
 $634万
 $23,552/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -25867,7 +25867,7 @@
           <t>H | 320呎 (2房)
 $712万
 $22,259/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -25875,7 +25875,7 @@
           <t>J | 269呎 (1房)
 $589万
 $21,894/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -25883,7 +25883,7 @@
           <t>K | 272呎 (1房)
 $596万
 $21,928/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -25891,7 +25891,7 @@
           <t>L | 272呎 (1房)
 $598万
 $22,000/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
@@ -25899,7 +25899,7 @@
           <t>M | 271呎 (1房)
 $593万
 $21,881/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="N5" s="23" t="inlineStr"/>
@@ -25917,7 +25917,7 @@
           <t>A | 465呎 (3房)
 $1003万
 $21,571/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>B | 349呎 (2房)
 $825万
 $23,632/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -25933,7 +25933,7 @@
           <t>C | 349呎 (2房)
 $785万
 $22,488/呎
-(26年-05月)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -25941,7 +25941,7 @@
           <t>D | 349呎 (2房)
 $712万
 $20,409/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -25949,7 +25949,7 @@
           <t>E | 350呎 (2房)
 $744万
 $21,246/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -25957,7 +25957,7 @@
           <t>F | 269呎 (1房)
 $596万
 $22,162/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -25965,7 +25965,7 @@
           <t>G | 269呎 (1房)
 $588万
 $21,873/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -25973,7 +25973,7 @@
           <t>H | 379呎 (2房)
 $865万
 $22,815/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -25981,7 +25981,7 @@
           <t>J | 320呎 (2房)
 $662万
 $20,672/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -25989,7 +25989,7 @@
           <t>K | 269呎 (1房)
 $547万
 $20,333/呎
-(26年-03月)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -25997,7 +25997,7 @@
           <t>L | 272呎 (1房)
 $531万
 $19,516/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -26005,7 +26005,7 @@
           <t>M | 272呎 (1房)
 $561万
 $20,632/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -26013,7 +26013,7 @@
           <t>N | 272呎 (1房)
 $572万
 $21,044/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -26021,7 +26021,7 @@
           <t>P | 268呎 (1房)
 $566万
 $21,121/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -26029,7 +26029,7 @@
           <t>Q | 367呎 (2房)
 $807万
 $21,981/呎
-(26年-05月)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -26044,7 +26044,7 @@
           <t>A | 465呎 (3房)
 $924万
 $19,879/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -26052,7 +26052,7 @@
           <t>B | 349呎 (2房)
 $749万
 $21,457/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -26060,7 +26060,7 @@
           <t>C | 349呎 (2房)
 $725万
 $20,776/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -26068,7 +26068,7 @@
           <t>D | 349呎 (2房)
 $697万
 $19,958/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -26076,7 +26076,7 @@
           <t>E | 350呎 (2房)
 $712万
 $20,332/呎
-(26年-03月)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -26084,7 +26084,7 @@
           <t>F | 269呎 (1房)
 $571万
 $21,230/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -26092,7 +26092,7 @@
           <t>G | 269呎 (1房)
 $564万
 $20,956/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -26100,7 +26100,7 @@
           <t>H | 379呎 (2房)
 $808万
 $21,306/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -26108,7 +26108,7 @@
           <t>J | 320呎 (2房)
 $632万
 $19,746/呎
-(26年-02月)</t>
+(26年-02月-28日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -26116,7 +26116,7 @@
           <t>K | 269呎 (1房)
 $550万
 $20,454/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -26124,7 +26124,7 @@
           <t>L | 272呎 (1房)
 $510万
 $18,748/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -26132,7 +26132,7 @@
           <t>M | 272呎 (1房)
 $536万
 $19,710/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -26140,7 +26140,7 @@
           <t>N | 272呎 (1房)
 $547万
 $20,102/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -26148,7 +26148,7 @@
           <t>P | 268呎 (1房)
 $541万
 $20,169/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
@@ -26156,7 +26156,7 @@
           <t>Q | 367呎 (2房)
 $779万
 $21,233/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
     </row>
@@ -26171,7 +26171,7 @@
           <t>A | 465呎 (3房)
 $929万
 $19,989/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -26179,7 +26179,7 @@
           <t>B | 349呎 (2房)
 $745万
 $21,334/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -26187,7 +26187,7 @@
           <t>C | 349呎 (2房)
 $721万
 $20,658/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -26195,7 +26195,7 @@
           <t>D | 349呎 (2房)
 $693万
 $19,844/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -26203,7 +26203,7 @@
           <t>E | 350呎 (2房)
 $745万
 $21,298/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -26211,7 +26211,7 @@
           <t>F | 269呎 (1房)
 $598万
 $22,245/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -26219,7 +26219,7 @@
           <t>G | 269呎 (1房)
 $552万
 $20,507/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -26227,7 +26227,7 @@
           <t>H | 379呎 (2房)
 $803万
 $21,184/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -26235,7 +26235,7 @@
           <t>J | 320呎 (2房)
 $630万
 $19,690/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -26243,7 +26243,7 @@
           <t>K | 269呎 (1房)
 $523万
 $19,460/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -26251,7 +26251,7 @@
           <t>L | 272呎 (1房)
 $522万
 $19,199/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -26259,7 +26259,7 @@
           <t>M | 272呎 (1房)
 $563万
 $20,703/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -26267,7 +26267,7 @@
           <t>N | 272呎 (1房)
 $545万
 $20,044/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="O8" s="21" t="inlineStr">
@@ -26275,7 +26275,7 @@
           <t>P | 268呎 (1房)
 $539万
 $20,109/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -26283,7 +26283,7 @@
           <t>Q | 367呎 (2房)
 $769万
 $20,947/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -26298,7 +26298,7 @@
           <t>A | 465呎 (3房)
 $940万
 $20,207/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -26306,7 +26306,7 @@
           <t>B | 349呎 (2房)
 $740万
 $21,213/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -26314,7 +26314,7 @@
           <t>C | 349呎 (2房)
 $717万
 $20,540/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -26322,7 +26322,7 @@
           <t>D | 349呎 (2房)
 $689万
 $19,731/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -26330,7 +26330,7 @@
           <t>E | 350呎 (2房)
 $704万
 $20,102/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -26338,7 +26338,7 @@
           <t>F | 269呎 (1房)
 $565万
 $20,997/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -26346,7 +26346,7 @@
           <t>G | 269呎 (1房)
 $540万
 $20,061/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -26354,7 +26354,7 @@
           <t>H | 379呎 (2房)
 $760万
 $20,061/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -26362,7 +26362,7 @@
           <t>J | 320呎 (2房)
 $628万
 $19,632/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -26370,7 +26370,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,301/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -26378,7 +26378,7 @@
           <t>L | 272呎 (1房)
 $493万
 $18,136/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -26386,7 +26386,7 @@
           <t>M | 272呎 (1房)
 $539万
 $19,807/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -26394,7 +26394,7 @@
           <t>N | 272呎 (1房)
 $573万
 $21,054/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -26402,7 +26402,7 @@
           <t>P | 268呎 (1房)
 $543万
 $20,265/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -26410,7 +26410,7 @@
           <t>Q | 367呎 (2房)
 $767万
 $20,886/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
     </row>
@@ -26425,7 +26425,7 @@
           <t>A | 465呎 (3房)
 $914万
 $19,657/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -26433,7 +26433,7 @@
           <t>B | 349呎 (2房)
 $740万
 $21,213/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -26441,7 +26441,7 @@
           <t>C | 349呎 (2房)
 $717万
 $20,540/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -26449,7 +26449,7 @@
           <t>D | 349呎 (2房)
 $711万
 $20,374/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -26457,7 +26457,7 @@
           <t>E | 350呎 (2房)
 $704万
 $20,102/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -26465,7 +26465,7 @@
           <t>F | 269呎 (1房)
 $565万
 $20,997/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -26473,7 +26473,7 @@
           <t>G | 269呎 (1房)
 $558万
 $20,726/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -26481,7 +26481,7 @@
           <t>H | 379呎 (2房)
 $790万
 $20,841/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -26489,7 +26489,7 @@
           <t>J | 320呎 (2房)
 $628万
 $19,632/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -26497,7 +26497,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,301/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -26505,7 +26505,7 @@
           <t>L | 272呎 (1房)
 $493万
 $18,136/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -26513,7 +26513,7 @@
           <t>M | 272呎 (1房)
 $533万
 $19,597/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -26521,7 +26521,7 @@
           <t>N | 272呎 (1房)
 $544万
 $19,985/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>P | 268呎 (1房)
 $540万
 $20,157/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -26537,7 +26537,7 @@
           <t>Q | 367呎 (2房)
 $808万
 $22,003/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -26552,7 +26552,7 @@
           <t>A | 465呎 (3房)
 $909万
 $19,544/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -26560,7 +26560,7 @@
           <t>B | 349呎 (2房)
 $732万
 $20,966/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -26568,7 +26568,7 @@
           <t>C | 349呎 (2房)
 $709万
 $20,305/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -26576,7 +26576,7 @@
           <t>D | 349呎 (2房)
 $703万
 $20,143/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>E | 350呎 (2房)
 $703万
 $20,085/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -26592,7 +26592,7 @@
           <t>F | 269呎 (1房)
 $588万
 $21,875/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -26600,7 +26600,7 @@
           <t>G | 269呎 (1房)
 $551万
 $20,497/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -26608,7 +26608,7 @@
           <t>H | 379呎 (2房)
 $781万
 $20,602/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -26616,7 +26616,7 @@
           <t>J | 320呎 (2房)
 $624万
 $19,515/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -26624,7 +26624,7 @@
           <t>K | 269呎 (1房)
 $516万
 $19,187/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -26632,7 +26632,7 @@
           <t>L | 272呎 (1房)
 $529万
 $19,432/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>M | 272呎 (1房)
 $536万
 $19,689/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>N | 272呎 (1房)
 $540万
 $19,869/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>P | 268呎 (1房)
 $534万
 $19,931/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>Q | 367呎 (2房)
 $803万
 $21,874/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
     </row>
@@ -26679,7 +26679,7 @@
           <t>A | 465呎 (3房)
 $899万
 $19,326/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -26687,7 +26687,7 @@
           <t>B | 349呎 (2房)
 $713万
 $20,439/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -26695,7 +26695,7 @@
           <t>C | 349呎 (2房)
 $715万
 $20,492/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -26703,7 +26703,7 @@
           <t>D | 349呎 (2房)
 $699万
 $20,026/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -26711,7 +26711,7 @@
           <t>E | 350呎 (2房)
 $688万
 $19,652/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -26719,7 +26719,7 @@
           <t>F | 269呎 (1房)
 $555万
 $20,650/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -26727,7 +26727,7 @@
           <t>G | 269呎 (1房)
 $548万
 $20,382/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -26735,7 +26735,7 @@
           <t>H | 379呎 (2房)
 $804万
 $21,206/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -26743,7 +26743,7 @@
           <t>J | 320呎 (2房)
 $626万
 $19,561/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -26751,7 +26751,7 @@
           <t>K | 269呎 (1房)
 $515万
 $19,128/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -26759,7 +26759,7 @@
           <t>L | 272呎 (1房)
 $511万
 $18,776/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -26767,7 +26767,7 @@
           <t>M | 272呎 (1房)
 $534万
 $19,629/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -26775,7 +26775,7 @@
           <t>N | 272呎 (1房)
 $568万
 $20,869/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -26783,7 +26783,7 @@
           <t>P | 268呎 (1房)
 $533万
 $19,872/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -26791,7 +26791,7 @@
           <t>Q | 367呎 (2房)
 $760万
 $20,702/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -26806,7 +26806,7 @@
           <t>A | 465呎 (3房)
 $933万
 $20,069/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -26814,7 +26814,7 @@
           <t>B | 349呎 (2房)
 $709万
 $20,318/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -26822,7 +26822,7 @@
           <t>C | 349呎 (2房)
 $711万
 $20,374/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -26830,7 +26830,7 @@
           <t>D | 349呎 (2房)
 $658万
 $18,861/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -26838,7 +26838,7 @@
           <t>E | 350呎 (2房)
 $662万
 $18,908/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -26846,7 +26846,7 @@
           <t>F | 269呎 (1房)
 $552万
 $20,532/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -26854,7 +26854,7 @@
           <t>G | 269呎 (1房)
 $551万
 $20,484/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -26862,7 +26862,7 @@
           <t>H | 379呎 (2房)
 $799万
 $21,083/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -26870,7 +26870,7 @@
           <t>J | 320呎 (2房)
 $619万
 $19,343/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -26878,7 +26878,7 @@
           <t>K | 269呎 (1房)
 $511万
 $19,013/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -26886,7 +26886,7 @@
           <t>L | 272呎 (1房)
 $489万
 $17,967/呎
-(25年-11月)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -26894,7 +26894,7 @@
           <t>M | 272呎 (1房)
 $525万
 $19,308/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -26902,7 +26902,7 @@
           <t>N | 272呎 (1房)
 $536万
 $19,693/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -26910,7 +26910,7 @@
           <t>P | 268呎 (1房)
 $532万
 $19,856/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="P13" s="21" t="inlineStr">
@@ -26918,7 +26918,7 @@
           <t>Q | 367呎 (2房)
 $758万
 $20,641/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -26933,7 +26933,7 @@
           <t>A | 465呎 (3房)
 $933万
 $20,058/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -26941,7 +26941,7 @@
           <t>B | 349呎 (2房)
 $705万
 $20,200/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -26949,7 +26949,7 @@
           <t>C | 349呎 (2房)
 $707万
 $20,254/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -26957,7 +26957,7 @@
           <t>D | 349呎 (2房)
 $654万
 $18,750/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -26965,7 +26965,7 @@
           <t>E | 350呎 (2房)
 $658万
 $18,800/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -26973,7 +26973,7 @@
           <t>F | 269呎 (1房)
 $549万
 $20,417/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -26981,7 +26981,7 @@
           <t>G | 269呎 (1房)
 $542万
 $20,153/呎
-(26年-04月)</t>
+(26年-04月-07日)</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -26989,7 +26989,7 @@
           <t>H | 379呎 (2房)
 $794万
 $20,960/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -26997,7 +26997,7 @@
           <t>J | 320呎 (2房)
 $655万
 $20,460/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -27005,7 +27005,7 @@
           <t>K | 269呎 (1房)
 $508万
 $18,898/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -27013,7 +27013,7 @@
           <t>L | 272呎 (1房)
 $488万
 $17,959/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -27021,7 +27021,7 @@
           <t>M | 272呎 (1房)
 $528万
 $19,397/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -27029,7 +27029,7 @@
           <t>N | 272呎 (1房)
 $561万
 $20,619/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -27037,7 +27037,7 @@
           <t>P | 268呎 (1房)
 $526万
 $19,631/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -27045,7 +27045,7 @@
           <t>Q | 367呎 (2房)
 $741万
 $20,180/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
           <t>A | 465呎 (3房)
 $883万
 $18,993/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>B | 349呎 (2房)
 $727万
 $20,837/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -27076,7 +27076,7 @@
           <t>C | 349呎 (2房)
 $700万
 $20,045/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -27084,7 +27084,7 @@
           <t>D | 349呎 (2房)
 $687万
 $19,675/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -27092,7 +27092,7 @@
           <t>E | 350呎 (2房)
 $654万
 $18,689/呎
-(25年-09月)</t>
+(25年-09月-13日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -27100,7 +27100,7 @@
           <t>F | 269呎 (1房)
 $557万
 $20,702/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -27108,7 +27108,7 @@
           <t>G | 269呎 (1房)
 $539万
 $20,038/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="I15" s="21" t="inlineStr">
@@ -27116,7 +27116,7 @@
           <t>H | 379呎 (2房)
 $790万
 $20,836/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -27124,7 +27124,7 @@
           <t>J | 320呎 (2房)
 $646万
 $20,192/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -27132,7 +27132,7 @@
           <t>K | 269呎 (1房)
 $507万
 $18,842/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -27140,7 +27140,7 @@
           <t>L | 272呎 (1房)
 $482万
 $17,709/呎
-(25年-11月)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -27148,7 +27148,7 @@
           <t>M | 272呎 (1房)
 $531万
 $19,514/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -27156,7 +27156,7 @@
           <t>N | 272呎 (1房)
 $531万
 $19,514/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -27164,7 +27164,7 @@
           <t>P | 268呎 (1房)
 $525万
 $19,572/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -27172,7 +27172,7 @@
           <t>Q | 367呎 (2房)
 $742万
 $20,226/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -27187,7 +27187,7 @@
           <t>A | 465呎 (3房)
 $878万
 $18,883/呎
-(25年-12月)</t>
+(25年-12月-28日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -27195,7 +27195,7 @@
           <t>B | 349呎 (2房)
 $686万
 $19,662/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -27203,7 +27203,7 @@
           <t>C | 349呎 (2房)
 $688万
 $19,715/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -27211,7 +27211,7 @@
           <t>D | 349呎 (2房)
 $647万
 $18,529/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -27219,7 +27219,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,579/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -27227,7 +27227,7 @@
           <t>F | 269呎 (1房)
 $554万
 $20,584/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -27235,7 +27235,7 @@
           <t>G | 269呎 (1房)
 $536万
 $19,923/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -27243,7 +27243,7 @@
           <t>H | 379呎 (2房)
 $785万
 $20,713/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -27251,7 +27251,7 @@
           <t>J | 320呎 (2房)
 $595万
 $18,601/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -27259,7 +27259,7 @@
           <t>K | 269呎 (1房)
 $505万
 $18,783/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -27267,7 +27267,7 @@
           <t>L | 272呎 (1房)
 $486万
 $17,852/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -27275,7 +27275,7 @@
           <t>M | 272呎 (1房)
 $529万
 $19,456/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -27283,7 +27283,7 @@
           <t>N | 272呎 (1房)
 $558万
 $20,497/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="O16" s="21" t="inlineStr">
@@ -27291,7 +27291,7 @@
           <t>P | 268呎 (1房)
 $523万
 $19,513/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="P16" s="21" t="inlineStr">
@@ -27299,7 +27299,7 @@
           <t>Q | 367呎 (2房)
 $736万
 $20,060/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
     </row>
@@ -27314,7 +27314,7 @@
           <t>A | 465呎 (3房)
 $850万
 $18,283/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -27322,7 +27322,7 @@
           <t>B | 349呎 (2房)
 $682万
 $19,544/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -27330,7 +27330,7 @@
           <t>C | 349呎 (2房)
 $691万
 $19,807/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -27338,7 +27338,7 @@
           <t>D | 349呎 (2房)
 $678万
 $19,441/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -27346,7 +27346,7 @@
           <t>E | 350呎 (2房)
 $646万
 $18,468/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -27354,7 +27354,7 @@
           <t>F | 269呎 (1房)
 $551万
 $20,465/呎
-(26年-05月)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -27362,7 +27362,7 @@
           <t>G | 269呎 (1房)
 $533万
 $19,809/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -27370,7 +27370,7 @@
           <t>H | 379呎 (2房)
 $725万
 $19,142/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -27378,7 +27378,7 @@
           <t>J | 320呎 (2房)
 $600万
 $18,748/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -27386,7 +27386,7 @@
           <t>K | 269呎 (1房)
 $504万
 $18,728/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -27394,7 +27394,7 @@
           <t>L | 272呎 (1房)
 $505万
 $18,581/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -27402,7 +27402,7 @@
           <t>M | 272呎 (1房)
 $528万
 $19,398/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -27410,7 +27410,7 @@
           <t>N | 272呎 (1房)
 $528万
 $19,398/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
@@ -27418,7 +27418,7 @@
           <t>P | 268呎 (1房)
 $521万
 $19,453/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="P17" s="21" t="inlineStr">
@@ -27426,7 +27426,7 @@
           <t>Q | 367呎 (2房)
 $734万
 $19,999/呎
-(26年-03月)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -27441,7 +27441,7 @@
           <t>A | 465呎 (3房)
 $916万
 $19,699/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -27449,7 +27449,7 @@
           <t>B | 349呎 (2房)
 $678万
 $19,426/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -27457,7 +27457,7 @@
           <t>C | 349呎 (2房)
 $680万
 $19,479/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -27465,7 +27465,7 @@
           <t>D | 349呎 (2房)
 $646万
 $18,513/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -27473,7 +27473,7 @@
           <t>E | 350呎 (2房)
 $678万
 $19,377/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -27481,7 +27481,7 @@
           <t>F | 269呎 (1房)
 $547万
 $20,347/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -27489,7 +27489,7 @@
           <t>G | 269呎 (1房)
 $558万
 $20,747/呎
-(26年-03月)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -27497,7 +27497,7 @@
           <t>H | 379呎 (2房)
 $749万
 $19,766/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -27505,7 +27505,7 @@
           <t>J | 320呎 (2房)
 $598万
 $18,690/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -27513,7 +27513,7 @@
           <t>K | 269呎 (1房)
 $502万
 $18,668/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -27521,7 +27521,7 @@
           <t>L | 272呎 (1房)
 $504万
 $18,525/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -27529,7 +27529,7 @@
           <t>M | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -27537,7 +27537,7 @@
           <t>N | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -27545,7 +27545,7 @@
           <t>P | 268呎 (1房)
 $520万
 $19,394/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="P18" s="21" t="inlineStr">
@@ -27553,7 +27553,7 @@
           <t>Q | 367呎 (2房)
 $707万
 $19,270/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
     </row>
@@ -27568,7 +27568,7 @@
           <t>A | 465呎 (3房)
 $916万
 $19,699/呎
-(25年-09月)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -27576,7 +27576,7 @@
           <t>B | 349呎 (2房)
 $667万
 $19,114/呎
-(26年-01月)</t>
+(26年-01月-11日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -27584,7 +27584,7 @@
           <t>C | 349呎 (2房)
 $669万
 $19,167/呎
-(26年-02月)</t>
+(26年-02月-22日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -27592,7 +27592,7 @@
           <t>D | 349呎 (2房)
 $639万
 $18,309/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -27600,7 +27600,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,561/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -27608,7 +27608,7 @@
           <t>F | 269呎 (1房)
 $547万
 $20,347/呎
-(26年-05月)</t>
+(26年-05月-17日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -27616,7 +27616,7 @@
           <t>G | 269呎 (1房)
 $530万
 $19,694/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -27624,7 +27624,7 @@
           <t>H | 379呎 (2房)
 $789万
 $20,823/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -27632,7 +27632,7 @@
           <t>J | 320呎 (2房)
 $640万
 $20,011/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -27640,7 +27640,7 @@
           <t>K | 269呎 (1房)
 $502万
 $18,668/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -27648,7 +27648,7 @@
           <t>L | 272呎 (1房)
 $504万
 $18,525/呎
-(25年-09月)</t>
+(25年-09月-13日)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -27656,7 +27656,7 @@
           <t>M | 272呎 (1房)
 $526万
 $19,339/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -27664,7 +27664,7 @@
           <t>N | 272呎 (1房)
 $532万
 $19,546/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
@@ -27672,7 +27672,7 @@
           <t>P | 268呎 (1房)
 $520万
 $19,394/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="P19" s="21" t="inlineStr">
@@ -27680,7 +27680,7 @@
           <t>Q | 367呎 (2房)
 $726万
 $19,793/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -27695,7 +27695,7 @@
           <t>A | 465呎 (3房)
 $862万
 $18,542/呎
-(25年-11月)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -27703,7 +27703,7 @@
           <t>B | 349呎 (2房)
 $659万
 $18,882/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -27711,7 +27711,7 @@
           <t>C | 349呎 (2房)
 $661万
 $18,935/呎
-(26年-01月)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -27719,7 +27719,7 @@
           <t>D | 349呎 (2房)
 $631万
 $18,088/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -27727,7 +27727,7 @@
           <t>E | 350呎 (2房)
 $635万
 $18,139/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -27735,7 +27735,7 @@
           <t>F | 269呎 (1房)
 $533万
 $19,824/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -27743,7 +27743,7 @@
           <t>G | 269呎 (1房)
 $524万
 $19,465/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -27751,7 +27751,7 @@
           <t>H | 379呎 (2房)
 $740万
 $19,529/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -27759,7 +27759,7 @@
           <t>J | 320呎 (2房)
 $627万
 $19,585/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -27767,7 +27767,7 @@
           <t>K | 269呎 (1房)
 $499万
 $18,554/呎
-(26年-03月)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>L | 272呎 (1房)
 $501万
 $18,413/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>M | 272呎 (1房)
 $513万
 $18,848/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -27791,7 +27791,7 @@
           <t>N | 272呎 (1房)
 $551万
 $20,250/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -27799,7 +27799,7 @@
           <t>P | 268呎 (1房)
 $522万
 $19,482/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="P20" s="21" t="inlineStr">
@@ -27807,7 +27807,7 @@
           <t>Q | 367呎 (2房)
 $721万
 $19,657/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -27822,7 +27822,7 @@
           <t>A | 465呎 (3房)
 $900万
 $19,347/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr">
@@ -27830,7 +27830,7 @@
           <t>B | 349呎 (2房)
 $655万
 $18,766/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="D21" s="21" t="inlineStr">
@@ -27838,7 +27838,7 @@
           <t>C | 349呎 (2房)
 $664万
 $19,023/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -27846,7 +27846,7 @@
           <t>D | 349呎 (2房)
 $627万
 $17,977/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -27854,7 +27854,7 @@
           <t>E | 350呎 (2房)
 $631万
 $18,028/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -27862,7 +27862,7 @@
           <t>F | 269呎 (1房)
 $527万
 $19,600/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -27870,7 +27870,7 @@
           <t>G | 269呎 (1房)
 $548万
 $20,384/呎
-(26年-03月)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -27878,7 +27878,7 @@
           <t>H | 379呎 (2房)
 $743万
 $19,616/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -27886,7 +27886,7 @@
           <t>J | 320呎 (2房)
 $599万
 $18,722/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="K21" s="21" t="inlineStr">
@@ -27894,7 +27894,7 @@
           <t>K | 269呎 (1房)
 $498万
 $18,498/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="L21" s="21" t="inlineStr">
@@ -27902,7 +27902,7 @@
           <t>L | 272呎 (1房)
 $499万
 $18,357/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="M21" s="21" t="inlineStr">
@@ -27910,7 +27910,7 @@
           <t>M | 272呎 (1房)
 $517万
 $18,990/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="N21" s="21" t="inlineStr">
@@ -27918,7 +27918,7 @@
           <t>N | 272呎 (1房)
 $521万
 $19,164/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="O21" s="21" t="inlineStr">
@@ -27926,7 +27926,7 @@
           <t>P | 268呎 (1房)
 $515万
 $19,216/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="P21" s="21" t="inlineStr">
@@ -27934,7 +27934,7 @@
           <t>Q | 367呎 (2房)
 $694万
 $18,921/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -27949,7 +27949,7 @@
           <t>A | 465呎 (3房)
 $894万
 $19,231/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C22" s="21" t="inlineStr">
@@ -27957,7 +27957,7 @@
           <t>B | 349呎 (2房)
 $672万
 $19,258/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="D22" s="21" t="inlineStr">
@@ -27965,7 +27965,7 @@
           <t>C | 349呎 (2房)
 $646万
 $18,500/呎
-(25年-11月)</t>
+(25年-11月-09日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -27973,7 +27973,7 @@
           <t>D | 349呎 (2房)
 $624万
 $17,866/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -27981,7 +27981,7 @@
           <t>E | 350呎 (2房)
 $662万
 $18,913/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -27989,7 +27989,7 @@
           <t>F | 269呎 (1房)
 $524万
 $19,486/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -27997,7 +27997,7 @@
           <t>G | 269呎 (1房)
 $523万
 $19,441/呎
-(26年-03月)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="I22" s="21" t="inlineStr">
@@ -28005,7 +28005,7 @@
           <t>H | 379呎 (2房)
 $731万
 $19,289/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -28013,7 +28013,7 @@
           <t>J | 320呎 (2房)
 $574万
 $17,949/呎
-(25年-12月)</t>
+(25年-12月-07日)</t>
         </is>
       </c>
       <c r="K22" s="21" t="inlineStr">
@@ -28021,7 +28021,7 @@
           <t>K | 269呎 (1房)
 $519万
 $19,304/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="L22" s="21" t="inlineStr">
@@ -28029,7 +28029,7 @@
           <t>L | 272呎 (1房)
 $469万
 $17,232/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="M22" s="21" t="inlineStr">
@@ -28037,7 +28037,7 @@
           <t>M | 272呎 (1房)
 $506万
 $18,617/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="N22" s="21" t="inlineStr">
@@ -28045,7 +28045,7 @@
           <t>N | 272呎 (1房)
 $516万
 $18,989/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="O22" s="21" t="inlineStr">
@@ -28053,7 +28053,7 @@
           <t>P | 268呎 (1房)
 $510万
 $19,035/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="P22" s="21" t="inlineStr">
@@ -28061,7 +28061,7 @@
           <t>Q | 367呎 (2房)
 $728万
 $19,828/呎
-(26年-03月)</t>
+(26年-03月-01日)</t>
         </is>
       </c>
     </row>
@@ -28076,7 +28076,7 @@
           <t>A | 465呎 (3房)
 $889万
 $19,114/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="C23" s="21" t="inlineStr">
@@ -28084,7 +28084,7 @@
           <t>B | 349呎 (2房)
 $668万
 $19,139/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D23" s="21" t="inlineStr">
@@ -28092,7 +28092,7 @@
           <t>C | 349呎 (2房)
 $634万
 $18,162/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -28100,7 +28100,7 @@
           <t>D | 349呎 (2房)
 $620万
 $17,755/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -28108,7 +28108,7 @@
           <t>E | 350呎 (2房)
 $665万
 $18,994/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -28116,7 +28116,7 @@
           <t>F | 269呎 (1房)
 $521万
 $19,367/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -28124,7 +28124,7 @@
           <t>G | 269呎 (1房)
 $514万
 $19,120/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -28132,7 +28132,7 @@
           <t>H | 379呎 (2房)
 $734万
 $19,374/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -28140,7 +28140,7 @@
           <t>J | 320呎 (2房)
 $585万
 $18,291/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="K23" s="21" t="inlineStr">
@@ -28148,7 +28148,7 @@
           <t>K | 269呎 (1房)
 $491万
 $18,269/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L23" s="21" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>L | 272呎 (1房)
 $467万
 $17,179/呎
-(25年-09月)</t>
+(25年-09月-28日)</t>
         </is>
       </c>
       <c r="M23" s="21" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>M | 272呎 (1房)
 $505万
 $18,559/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="N23" s="21" t="inlineStr">
@@ -28172,7 +28172,7 @@
           <t>N | 272呎 (1房)
 $518万
 $19,031/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="O23" s="21" t="inlineStr">
@@ -28180,7 +28180,7 @@
           <t>P | 268呎 (1房)
 $509万
 $18,975/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="P23" s="21" t="inlineStr">
@@ -28188,7 +28188,7 @@
           <t>Q | 367呎 (2房)
 $671万
 $18,284/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
     </row>
@@ -28203,7 +28203,7 @@
           <t>A | 465呎 (3房)
 $832万
 $17,886/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="C24" s="21" t="inlineStr">
@@ -28211,7 +28211,7 @@
           <t>B | 349呎 (2房)
 $625万
 $17,905/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -28219,7 +28219,7 @@
           <t>C | 349呎 (2房)
 $661万
 $18,926/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -28227,7 +28227,7 @@
           <t>D | 349呎 (2房)
 $646万
 $18,510/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -28235,7 +28235,7 @@
           <t>E | 350呎 (2房)
 $650万
 $18,563/呎
-(25年-09月)</t>
+(25年-09月-13日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -28243,7 +28243,7 @@
           <t>F | 269呎 (1房)
 $515万
 $19,134/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -28251,7 +28251,7 @@
           <t>G | 269呎 (1房)
 $508万
 $18,891/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="I24" s="21" t="inlineStr">
@@ -28259,7 +28259,7 @@
           <t>H | 379呎 (2房)
 $756万
 $19,944/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -28267,7 +28267,7 @@
           <t>J | 320呎 (2房)
 $571万
 $17,840/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="K24" s="21" t="inlineStr">
@@ -28275,7 +28275,7 @@
           <t>K | 269呎 (1房)
 $492万
 $18,307/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L24" s="21" t="inlineStr">
@@ -28283,7 +28283,7 @@
           <t>L | 272呎 (1房)
 $492万
 $18,078/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="M24" s="21" t="inlineStr">
@@ -28291,7 +28291,7 @@
           <t>M | 272呎 (1房)
 $503万
 $18,500/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N24" s="21" t="inlineStr">
@@ -28299,7 +28299,7 @@
           <t>N | 272呎 (1房)
 $519万
 $19,070/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O24" s="21" t="inlineStr">
@@ -28307,7 +28307,7 @@
           <t>P | 268呎 (1房)
 $507万
 $18,916/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="P24" s="21" t="inlineStr">
@@ -28315,7 +28315,7 @@
           <t>Q | 367呎 (2房)
 $667万
 $18,172/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
     </row>
@@ -28330,7 +28330,7 @@
           <t>A | 465呎 (3房)
 $816万
 $17,555/呎
-(25年-10月)</t>
+(25年-10月-12日)</t>
         </is>
       </c>
       <c r="C25" s="21" t="inlineStr">
@@ -28338,7 +28338,7 @@
           <t>B | 349呎 (2房)
 $613万
 $17,564/呎
-(25年-12月)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="D25" s="21" t="inlineStr">
@@ -28346,7 +28346,7 @@
           <t>C | 349呎 (2房)
 $648万
 $18,567/呎
-(25年-10月)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -28354,7 +28354,7 @@
           <t>D | 349呎 (2房)
 $634万
 $18,159/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -28362,7 +28362,7 @@
           <t>E | 350呎 (2房)
 $638万
 $18,215/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -28370,7 +28370,7 @@
           <t>F | 269呎 (1房)
 $505万
 $18,787/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -28378,7 +28378,7 @@
           <t>G | 269呎 (1房)
 $488万
 $18,150/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -28386,7 +28386,7 @@
           <t>H | 379呎 (2房)
 $708万
 $18,671/呎
-(26年-03月)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -28394,7 +28394,7 @@
           <t>J | 320呎 (2房)
 $582万
 $18,178/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="K25" s="21" t="inlineStr">
@@ -28402,7 +28402,7 @@
           <t>K | 269呎 (1房)
 $488万
 $18,154/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L25" s="21" t="inlineStr">
@@ -28410,7 +28410,7 @@
           <t>L | 272呎 (1房)
 $490万
 $18,018/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="M25" s="21" t="inlineStr">
@@ -28418,7 +28418,7 @@
           <t>M | 272呎 (1房)
 $502万
 $18,446/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N25" s="21" t="inlineStr">
@@ -28426,7 +28426,7 @@
           <t>N | 272呎 (1房)
 $512万
 $18,810/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O25" s="21" t="inlineStr">
@@ -28434,7 +28434,7 @@
           <t>P | 268呎 (1房)
 $506万
 $18,892/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="P25" s="21" t="inlineStr">
@@ -28442,7 +28442,7 @@
           <t>Q | 367呎 (2房)
 $663万
 $18,056/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -28457,7 +28457,7 @@
           <t>A | 465呎 (3房)
 $818万
 $17,582/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C26" s="21" t="inlineStr">
@@ -28465,7 +28465,7 @@
           <t>B | 349呎 (2房)
 $621万
 $17,781/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="D26" s="21" t="inlineStr">
@@ -28473,7 +28473,7 @@
           <t>C | 349呎 (2房)
 $621万
 $17,807/呎
-(26年-01月)</t>
+(26年-01月-29日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -28481,7 +28481,7 @@
           <t>D | 349呎 (2房)
 $595万
 $17,038/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -28489,7 +28489,7 @@
           <t>E | 350呎 (2房)
 $631万
 $18,039/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -28497,7 +28497,7 @@
           <t>F | 269呎 (1房)
 $501万
 $18,609/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -28505,7 +28505,7 @@
           <t>G | 269呎 (1房)
 $492万
 $18,278/呎
-(26年-01月)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -28513,7 +28513,7 @@
           <t>H | 379呎 (2房)
 $734万
 $19,378/呎
-(26年-03月)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="J26" s="21" t="inlineStr">
@@ -28521,7 +28521,7 @@
           <t>J | 320呎 (2房)
 $567万
 $17,727/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="K26" s="21" t="inlineStr">
@@ -28529,7 +28529,7 @@
           <t>K | 269呎 (1房)
 $487万
 $18,095/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L26" s="21" t="inlineStr">
@@ -28537,7 +28537,7 @@
           <t>L | 272呎 (1房)
 $465万
 $17,112/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="M26" s="21" t="inlineStr">
@@ -28545,7 +28545,7 @@
           <t>M | 272呎 (1房)
 $500万
 $18,387/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="N26" s="21" t="inlineStr">
@@ -28553,7 +28553,7 @@
           <t>N | 272呎 (1房)
 $510万
 $18,751/呎
-(26年-04月)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="O26" s="21" t="inlineStr">
@@ -28561,7 +28561,7 @@
           <t>P | 268呎 (1房)
 $505万
 $18,832/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="P26" s="21" t="inlineStr">
@@ -28569,7 +28569,7 @@
           <t>Q | 367呎 (2房)
 $656万
 $17,887/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
     </row>
@@ -28584,7 +28584,7 @@
           <t>A | 465呎 (3房)
 $796万
 $17,122/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -28592,7 +28592,7 @@
           <t>B | 349呎 (2房)
 $621万
 $17,781/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -28600,7 +28600,7 @@
           <t>C | 349呎 (2房)
 $662万
 $18,968/呎
-(26年-01月)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -28608,7 +28608,7 @@
           <t>D | 349呎 (2房)
 $595万
 $17,038/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -28616,7 +28616,7 @@
           <t>E | 350呎 (2房)
 $598万
 $17,090/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -28624,7 +28624,7 @@
           <t>F | 269呎 (1房)
 $501万
 $18,609/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -28632,7 +28632,7 @@
           <t>G | 269呎 (1房)
 $486万
 $18,082/呎
-(26年-02月)</t>
+(26年-02月-15日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -28640,7 +28640,7 @@
           <t>H | 379呎 (2房)
 $705万
 $18,591/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -28648,7 +28648,7 @@
           <t>J | 320呎 (2房)
 $580万
 $18,121/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -28656,7 +28656,7 @@
           <t>K | 269呎 (1房)
 $487万
 $18,095/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -28664,7 +28664,7 @@
           <t>L | 272呎 (1房)
 $463万
 $17,017/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -28672,7 +28672,7 @@
           <t>M | 272呎 (1房)
 $500万
 $18,387/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -28680,7 +28680,7 @@
           <t>N | 272呎 (1房)
 $510万
 $18,751/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -28688,7 +28688,7 @@
           <t>P | 268呎 (1房)
 $532万
 $19,840/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="P27" s="21" t="inlineStr">
@@ -28696,7 +28696,7 @@
           <t>Q | 367呎 (2房)
 $671万
 $18,284/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -28711,7 +28711,7 @@
           <t>A | 465呎 (3房)
 $772万
 $16,610/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C28" s="21" t="inlineStr">
@@ -28719,7 +28719,7 @@
           <t>B | 349呎 (2房)
 $615万
 $17,622/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D28" s="21" t="inlineStr">
@@ -28727,7 +28727,7 @@
           <t>C | 349呎 (2房)
 $609万
 $17,459/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -28735,7 +28735,7 @@
           <t>D | 349呎 (2房)
 $622万
 $17,819/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -28743,7 +28743,7 @@
           <t>E | 350呎 (2房)
 $626万
 $17,878/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -28751,7 +28751,7 @@
           <t>F | 269呎 (1房)
 $491万
 $18,262/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -28759,7 +28759,7 @@
           <t>G | 269呎 (1房)
 $498万
 $18,514/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -28767,7 +28767,7 @@
           <t>H | 379呎 (2房)
 $658万
 $17,361/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">
@@ -28775,7 +28775,7 @@
           <t>J | 320呎 (2房)
 $576万
 $18,006/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -28783,7 +28783,7 @@
           <t>K | 269呎 (1房)
 $484万
 $17,980/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -28791,7 +28791,7 @@
           <t>L | 272呎 (1房)
 $491万
 $18,039/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -28799,7 +28799,7 @@
           <t>M | 272呎 (1房)
 $497万
 $18,270/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -28807,7 +28807,7 @@
           <t>N | 272呎 (1房)
 $516万
 $18,982/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -28815,7 +28815,7 @@
           <t>P | 268呎 (1房)
 $507万
 $18,914/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="P28" s="21" t="inlineStr">
@@ -28823,7 +28823,7 @@
           <t>Q | 367呎 (2房)
 $694万
 $18,914/呎
-(25年-12月)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
     </row>
@@ -28838,7 +28838,7 @@
           <t>A | 465呎 (3房)
 $765万
 $16,450/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="C29" s="21" t="inlineStr">
@@ -28846,7 +28846,7 @@
           <t>B | 349呎 (2房)
 $589万
 $16,883/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="D29" s="21" t="inlineStr">
@@ -28854,7 +28854,7 @@
           <t>C | 349呎 (2房)
 $623万
 $17,848/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -28862,7 +28862,7 @@
           <t>D | 349呎 (2房)
 $577万
 $16,540/呎
-(25年-10月)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -28870,7 +28870,7 @@
           <t>E | 350呎 (2房)
 $613万
 $17,518/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -28878,7 +28878,7 @@
           <t>F | 269呎 (1房)
 $492万
 $18,281/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -28886,7 +28886,7 @@
           <t>G | 269呎 (1房)
 $462万
 $17,190/呎
-(25年-10月)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -28894,7 +28894,7 @@
           <t>H | 379呎 (2房)
 $655万
 $17,283/呎
-(25年-10月)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="J29" s="21" t="inlineStr">
@@ -28902,7 +28902,7 @@
           <t>J | 320呎 (2房)
 $591万
 $18,478/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="K29" s="21" t="inlineStr">
@@ -28910,7 +28910,7 @@
           <t>K | 269呎 (1房)
 $482万
 $17,925/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="L29" s="21" t="inlineStr">
@@ -28918,7 +28918,7 @@
           <t>L | 272呎 (1房)
 $484万
 $17,795/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="M29" s="21" t="inlineStr">
@@ -28926,7 +28926,7 @@
           <t>M | 272呎 (1房)
 $522万
 $19,189/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="N29" s="21" t="inlineStr">
@@ -28934,7 +28934,7 @@
           <t>N | 272呎 (1房)
 $507万
 $18,628/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="O29" s="21" t="inlineStr">
@@ -28942,7 +28942,7 @@
           <t>P | 268呎 (1房)
 $505万
 $18,854/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="P29" s="21" t="inlineStr">
@@ -28950,7 +28950,7 @@
           <t>Q | 367呎 (2房)
 $645万
 $17,570/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -28965,7 +28965,7 @@
           <t>A | 465呎 (3房)
 $755万
 $16,233/呎
-(25年-10月)</t>
+(25年-10月-05日)</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -28973,7 +28973,7 @@
           <t>B | 349呎 (2房)
 $613万
 $17,563/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D30" s="21" t="inlineStr">
@@ -28981,7 +28981,7 @@
           <t>C | 349呎 (2房)
 $582万
 $16,682/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -28989,7 +28989,7 @@
           <t>D | 349呎 (2房)
 $569万
 $16,298/呎
-(25年-10月)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -28997,7 +28997,7 @@
           <t>E | 350呎 (2房)
 $573万
 $16,375/呎
-(25年-11月)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -29005,7 +29005,7 @@
           <t>F | 269呎 (1房)
 $487万
 $18,102/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -29013,7 +29013,7 @@
           <t>G | 269呎 (1房)
 $482万
 $17,905/呎
-(25年-10月)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -29021,7 +29021,7 @@
           <t>H | 379呎 (2房)
 $693万
 $18,276/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="J30" s="21" t="inlineStr">
@@ -29029,7 +29029,7 @@
           <t>J | 320呎 (2房)
 $557万
 $17,392/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="K30" s="21" t="inlineStr">
@@ -29037,7 +29037,7 @@
           <t>K | 269呎 (1房)
 $480万
 $17,848/呎
-(26年-03月)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="L30" s="21" t="inlineStr">
@@ -29045,7 +29045,7 @@
           <t>L | 272呎 (1房)
 $482万
 $17,708/呎
-(25年-10月)</t>
+(25年-10月-01日)</t>
         </is>
       </c>
       <c r="M30" s="21" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>M | 272呎 (1房)
 $494万
 $18,157/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="N30" s="21" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>N | 272呎 (1房)
 $505万
 $18,573/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="O30" s="21" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>P | 268呎 (1房)
 $499万
 $18,613/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="P30" s="21" t="inlineStr">
@@ -29077,7 +29077,7 @@
           <t>Q | 367呎 (2房)
 $632万
 $17,208/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -29092,7 +29092,7 @@
           <t>A | 428呎 (3房)
 $907万
 $21,200/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C31" s="21" t="inlineStr">
@@ -29100,7 +29100,7 @@
           <t>B | 312呎 (2房)
 $657万
 $21,051/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D31" s="21" t="inlineStr">
@@ -29108,7 +29108,7 @@
           <t>C | 312呎 (2房)
 $697万
 $22,330/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -29116,7 +29116,7 @@
           <t>D | 312呎 (2房)
 $669万
 $21,436/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -29124,7 +29124,7 @@
           <t>E | 312呎 (2房)
 $676万
 $21,672/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -29132,7 +29132,7 @@
           <t>F | 232呎 (1房)
 $536万
 $23,100/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -29140,7 +29140,7 @@
           <t>G | 231呎 (1房)
 $541万
 $23,400/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="I31" s="21" t="inlineStr">
@@ -29148,7 +29148,7 @@
           <t>H | 343呎 (2房)
 $909万
 $26,500/呎
-(26年-04月)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="J31" s="21" t="inlineStr">
@@ -29156,7 +29156,7 @@
           <t>J | 536呎 (3房)
 $1608万
 $30,000/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="K31" s="21" t="inlineStr">
@@ -29164,7 +29164,7 @@
           <t>K | 235呎 (1房)
 $790万
 $33,638/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="L31" s="21" t="inlineStr">
@@ -29172,7 +29172,7 @@
           <t>L | 235呎 (1房)
 $689万
 $29,300/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="M31" s="21" t="inlineStr">
@@ -29180,7 +29180,7 @@
           <t>M | 234呎 (1房)
 $716万
 $30,603/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N31" s="21" t="inlineStr">
@@ -29188,7 +29188,7 @@
           <t>N | 230呎 (1房)
 $639万
 $27,775/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="O31" s="21" t="inlineStr">
@@ -29196,7 +29196,7 @@
           <t>P | 328呎 (2房)
 $827万
 $25,200/呎
-(26年-06月)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="P31" s="23" t="inlineStr"/>
